--- a/Asistencias/Calificaciones.xlsx
+++ b/Asistencias/Calificaciones.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlosmartinez/Proyectos/Github/CalculoDiferencialTNM/Asistencias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC6F076-60F0-E247-9806-E73E914DF95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1C8266-F3F3-CF42-9A7C-6725C45B0624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="25980" windowHeight="17020" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11920" yWindow="660" windowWidth="18240" windowHeight="17180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5A_CD" sheetId="4" r:id="rId1"/>
@@ -3101,6 +3101,35 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3128,12 +3157,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3147,6 +3170,12 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3167,6 +3196,12 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="27" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3174,41 +3209,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="26" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3257,6 +3257,7 @@
           <cell r="C2" t="str">
             <v>NOMBRE ALUMNO</v>
           </cell>
+          <cell r="J2"/>
         </row>
         <row r="3">
           <cell r="C3" t="str">
@@ -4135,6 +4136,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="3">
+        <row r="7">
+          <cell r="C7"/>
+        </row>
         <row r="9">
           <cell r="C9" t="str">
             <v>NOMBRE ALUMNO</v>
@@ -5540,107 +5544,107 @@
       <c r="H1" s="18"/>
       <c r="I1" s="9"/>
       <c r="J1" s="52"/>
-      <c r="K1" s="89" t="s">
+      <c r="K1" s="102" t="s">
         <v>758</v>
       </c>
       <c r="L1" s="36"/>
-      <c r="M1" s="98" t="s">
+      <c r="M1" s="109" t="s">
         <v>759</v>
       </c>
-      <c r="N1" s="99"/>
-      <c r="O1" s="99"/>
-      <c r="P1" s="99"/>
-      <c r="Q1" s="99"/>
-      <c r="R1" s="100"/>
-      <c r="S1" s="101" t="s">
+      <c r="N1" s="110"/>
+      <c r="O1" s="110"/>
+      <c r="P1" s="110"/>
+      <c r="Q1" s="110"/>
+      <c r="R1" s="111"/>
+      <c r="S1" s="112" t="s">
         <v>760</v>
       </c>
-      <c r="T1" s="99"/>
-      <c r="U1" s="99"/>
-      <c r="V1" s="99"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="102"/>
-      <c r="Y1" s="98" t="s">
+      <c r="T1" s="110"/>
+      <c r="U1" s="110"/>
+      <c r="V1" s="110"/>
+      <c r="W1" s="110"/>
+      <c r="X1" s="113"/>
+      <c r="Y1" s="109" t="s">
         <v>761</v>
       </c>
-      <c r="Z1" s="99"/>
-      <c r="AA1" s="99"/>
-      <c r="AB1" s="99"/>
-      <c r="AC1" s="99"/>
-      <c r="AD1" s="99"/>
-      <c r="AE1" s="101" t="s">
+      <c r="Z1" s="110"/>
+      <c r="AA1" s="110"/>
+      <c r="AB1" s="110"/>
+      <c r="AC1" s="110"/>
+      <c r="AD1" s="110"/>
+      <c r="AE1" s="112" t="s">
         <v>762</v>
       </c>
-      <c r="AF1" s="99"/>
-      <c r="AG1" s="99"/>
-      <c r="AH1" s="99"/>
-      <c r="AI1" s="99"/>
-      <c r="AJ1" s="102"/>
-      <c r="AK1" s="88" t="s">
+      <c r="AF1" s="110"/>
+      <c r="AG1" s="110"/>
+      <c r="AH1" s="110"/>
+      <c r="AI1" s="110"/>
+      <c r="AJ1" s="113"/>
+      <c r="AK1" s="101" t="s">
         <v>765</v>
       </c>
-      <c r="AL1" s="88"/>
-      <c r="AM1" s="88"/>
-      <c r="AN1" s="88"/>
-      <c r="AO1" s="88"/>
-      <c r="AP1" s="88"/>
-      <c r="AQ1" s="87" t="s">
+      <c r="AL1" s="101"/>
+      <c r="AM1" s="101"/>
+      <c r="AN1" s="101"/>
+      <c r="AO1" s="101"/>
+      <c r="AP1" s="101"/>
+      <c r="AQ1" s="100" t="s">
         <v>766</v>
       </c>
-      <c r="AR1" s="88"/>
-      <c r="AS1" s="88"/>
-      <c r="AT1" s="88"/>
-      <c r="AU1" s="88"/>
-      <c r="AV1" s="88"/>
-      <c r="AW1" s="87" t="s">
+      <c r="AR1" s="101"/>
+      <c r="AS1" s="101"/>
+      <c r="AT1" s="101"/>
+      <c r="AU1" s="101"/>
+      <c r="AV1" s="101"/>
+      <c r="AW1" s="100" t="s">
         <v>767</v>
       </c>
-      <c r="AX1" s="88"/>
-      <c r="AY1" s="88"/>
-      <c r="AZ1" s="88"/>
-      <c r="BA1" s="88"/>
-      <c r="BB1" s="88"/>
-      <c r="BC1" s="87" t="s">
+      <c r="AX1" s="101"/>
+      <c r="AY1" s="101"/>
+      <c r="AZ1" s="101"/>
+      <c r="BA1" s="101"/>
+      <c r="BB1" s="101"/>
+      <c r="BC1" s="100" t="s">
         <v>768</v>
       </c>
-      <c r="BD1" s="88"/>
-      <c r="BE1" s="88"/>
-      <c r="BF1" s="88"/>
-      <c r="BG1" s="88"/>
-      <c r="BH1" s="88"/>
-      <c r="BI1" s="91"/>
-      <c r="BJ1" s="87" t="s">
+      <c r="BD1" s="101"/>
+      <c r="BE1" s="101"/>
+      <c r="BF1" s="101"/>
+      <c r="BG1" s="101"/>
+      <c r="BH1" s="101"/>
+      <c r="BI1" s="104"/>
+      <c r="BJ1" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="BK1" s="88"/>
-      <c r="BL1" s="88"/>
-      <c r="BM1" s="88"/>
-      <c r="BN1" s="88"/>
-      <c r="BO1" s="88"/>
-      <c r="BP1" s="87" t="s">
+      <c r="BK1" s="101"/>
+      <c r="BL1" s="101"/>
+      <c r="BM1" s="101"/>
+      <c r="BN1" s="101"/>
+      <c r="BO1" s="101"/>
+      <c r="BP1" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="BQ1" s="88"/>
-      <c r="BR1" s="88"/>
-      <c r="BS1" s="88"/>
-      <c r="BT1" s="88"/>
-      <c r="BU1" s="88"/>
-      <c r="BV1" s="87" t="s">
+      <c r="BQ1" s="101"/>
+      <c r="BR1" s="101"/>
+      <c r="BS1" s="101"/>
+      <c r="BT1" s="101"/>
+      <c r="BU1" s="101"/>
+      <c r="BV1" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="BW1" s="88"/>
-      <c r="BX1" s="88"/>
-      <c r="BY1" s="88"/>
-      <c r="BZ1" s="88"/>
-      <c r="CA1" s="88"/>
-      <c r="CB1" s="87" t="s">
+      <c r="BW1" s="101"/>
+      <c r="BX1" s="101"/>
+      <c r="BY1" s="101"/>
+      <c r="BZ1" s="101"/>
+      <c r="CA1" s="101"/>
+      <c r="CB1" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="CC1" s="88"/>
-      <c r="CD1" s="88"/>
-      <c r="CE1" s="88"/>
-      <c r="CF1" s="88"/>
-      <c r="CG1" s="88"/>
+      <c r="CC1" s="101"/>
+      <c r="CD1" s="101"/>
+      <c r="CE1" s="101"/>
+      <c r="CF1" s="101"/>
+      <c r="CG1" s="101"/>
     </row>
     <row r="2" spans="1:85" ht="48" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
@@ -5673,7 +5677,7 @@
       <c r="J2" s="24" t="s">
         <v>770</v>
       </c>
-      <c r="K2" s="90"/>
+      <c r="K2" s="103"/>
       <c r="L2" s="56" t="s">
         <v>772</v>
       </c>
@@ -5821,7 +5825,7 @@
       <c r="BH2" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="BI2" s="92"/>
+      <c r="BI2" s="105"/>
       <c r="BJ2" s="18" t="s">
         <v>752</v>
       </c>
@@ -5919,7 +5923,7 @@
         <f>_xlfn.XLOOKUP(C3,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I3" s="124">
+      <c r="I3" s="97">
         <f>J3*0.7+G3*20+H3*10</f>
         <v>70.775000000000006</v>
       </c>
@@ -6084,7 +6088,7 @@
         <f>AVERAGE(BC3:BG3)</f>
         <v>0</v>
       </c>
-      <c r="BI3" s="93"/>
+      <c r="BI3" s="106"/>
       <c r="BJ3" s="5"/>
       <c r="BK3" s="5"/>
       <c r="BL3" s="5"/>
@@ -6148,7 +6152,7 @@
         <f>_xlfn.XLOOKUP(C4,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>0.9285714285714286</v>
       </c>
-      <c r="I4" s="124">
+      <c r="I4" s="97">
         <f>J4*0.7+G4*20+H4*10</f>
         <v>79.685714285714297</v>
       </c>
@@ -6313,7 +6317,7 @@
         <f t="shared" ref="BH4:BH39" si="9">AVERAGE(BC4:BG4)</f>
         <v>0</v>
       </c>
-      <c r="BI4" s="94"/>
+      <c r="BI4" s="107"/>
       <c r="BJ4" s="7"/>
       <c r="BK4" s="7"/>
       <c r="BL4" s="7"/>
@@ -6377,7 +6381,7 @@
         <f>_xlfn.XLOOKUP(C5,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I5" s="124">
+      <c r="I5" s="97">
         <f>J5*0.7+G5*20+H5*10</f>
         <v>100</v>
       </c>
@@ -6542,7 +6546,7 @@
         <f t="shared" si="9"/>
         <v>0.5</v>
       </c>
-      <c r="BI5" s="94"/>
+      <c r="BI5" s="107"/>
       <c r="BJ5" s="5"/>
       <c r="BK5" s="5"/>
       <c r="BL5" s="5"/>
@@ -6604,8 +6608,8 @@
         <f>_xlfn.XLOOKUP(C6,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I6" s="124">
-        <f t="shared" ref="I4:I40" si="14">J6*0.7+G6*20+H6*10</f>
+      <c r="I6" s="97">
+        <f t="shared" ref="I6:I40" si="14">J6*0.7+G6*20+H6*10</f>
         <v>65.77</v>
       </c>
       <c r="J6" s="33">
@@ -6769,7 +6773,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="BI6" s="94"/>
+      <c r="BI6" s="107"/>
       <c r="BJ6" s="7"/>
       <c r="BK6" s="7"/>
       <c r="BL6" s="7"/>
@@ -6831,7 +6835,7 @@
         <f>_xlfn.XLOOKUP(C7,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I7" s="124">
+      <c r="I7" s="97">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
@@ -6996,7 +7000,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI7" s="94"/>
+      <c r="BI7" s="107"/>
       <c r="BJ7" s="5"/>
       <c r="BK7" s="5"/>
       <c r="BL7" s="5"/>
@@ -7049,7 +7053,7 @@
       <c r="F8" s="61"/>
       <c r="G8" s="61"/>
       <c r="H8" s="59"/>
-      <c r="I8" s="126" t="e">
+      <c r="I8" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -7134,7 +7138,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI8" s="94"/>
+      <c r="BI8" s="107"/>
       <c r="BJ8" s="61"/>
       <c r="BK8" s="61"/>
       <c r="BL8" s="61"/>
@@ -7187,7 +7191,7 @@
       <c r="F9" s="61"/>
       <c r="G9" s="61"/>
       <c r="H9" s="59"/>
-      <c r="I9" s="126" t="e">
+      <c r="I9" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -7272,7 +7276,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI9" s="94"/>
+      <c r="BI9" s="107"/>
       <c r="BJ9" s="61"/>
       <c r="BK9" s="61"/>
       <c r="BL9" s="61"/>
@@ -7334,7 +7338,7 @@
         <f>_xlfn.XLOOKUP(C10,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I10" s="124">
+      <c r="I10" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -7499,7 +7503,7 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="BI10" s="94"/>
+      <c r="BI10" s="107"/>
       <c r="BJ10" s="7"/>
       <c r="BK10" s="7"/>
       <c r="BL10" s="7"/>
@@ -7561,7 +7565,7 @@
         <f>_xlfn.XLOOKUP(C11,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -7728,7 +7732,7 @@
         <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
-      <c r="BI11" s="94"/>
+      <c r="BI11" s="107"/>
       <c r="BJ11" s="5"/>
       <c r="BK11" s="5"/>
       <c r="BL11" s="5"/>
@@ -7790,7 +7794,7 @@
         <f>_xlfn.XLOOKUP(C12,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="124">
+      <c r="I12" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -7955,7 +7959,7 @@
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
-      <c r="BI12" s="94"/>
+      <c r="BI12" s="107"/>
       <c r="BJ12" s="7"/>
       <c r="BK12" s="7"/>
       <c r="BL12" s="7"/>
@@ -8017,7 +8021,7 @@
         <f>_xlfn.XLOOKUP(C13,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I13" s="124">
+      <c r="I13" s="97">
         <f t="shared" si="14"/>
         <v>96.36</v>
       </c>
@@ -8182,7 +8186,7 @@
         <f t="shared" si="9"/>
         <v>0.48</v>
       </c>
-      <c r="BI13" s="94"/>
+      <c r="BI13" s="107"/>
       <c r="BJ13" s="5"/>
       <c r="BK13" s="5"/>
       <c r="BL13" s="5"/>
@@ -8240,7 +8244,7 @@
         <f>_xlfn.XLOOKUP(C14,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I14" s="124">
+      <c r="I14" s="97">
         <f t="shared" si="14"/>
         <v>44</v>
       </c>
@@ -8405,7 +8409,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI14" s="94"/>
+      <c r="BI14" s="107"/>
       <c r="BJ14" s="7"/>
       <c r="BK14" s="7"/>
       <c r="BL14" s="7"/>
@@ -8467,7 +8471,7 @@
         <f>_xlfn.XLOOKUP(C15,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I15" s="124">
+      <c r="I15" s="97">
         <f t="shared" si="14"/>
         <v>46.45</v>
       </c>
@@ -8632,7 +8636,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI15" s="94"/>
+      <c r="BI15" s="107"/>
       <c r="BJ15" s="5"/>
       <c r="BK15" s="5"/>
       <c r="BL15" s="5"/>
@@ -8694,7 +8698,7 @@
         <f>_xlfn.XLOOKUP(C16,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I16" s="124">
+      <c r="I16" s="97">
         <f t="shared" si="14"/>
         <v>63.074999999999996</v>
       </c>
@@ -8861,7 +8865,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI16" s="94"/>
+      <c r="BI16" s="107"/>
       <c r="BJ16" s="7">
         <v>0.75</v>
       </c>
@@ -8926,7 +8930,7 @@
       <c r="F17" s="61"/>
       <c r="G17" s="61"/>
       <c r="H17" s="59"/>
-      <c r="I17" s="126" t="e">
+      <c r="I17" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -9011,7 +9015,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI17" s="94"/>
+      <c r="BI17" s="107"/>
       <c r="BJ17" s="61"/>
       <c r="BK17" s="61"/>
       <c r="BL17" s="61"/>
@@ -9073,7 +9077,7 @@
         <f>_xlfn.XLOOKUP(C18,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I18" s="124">
+      <c r="I18" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -9240,7 +9244,7 @@
         <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="BI18" s="94"/>
+      <c r="BI18" s="107"/>
       <c r="BJ18" s="7">
         <v>1</v>
       </c>
@@ -9322,7 +9326,7 @@
         <f>_xlfn.XLOOKUP(C19,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="I19" s="124">
+      <c r="I19" s="97">
         <f t="shared" si="14"/>
         <v>81.657142857142858</v>
       </c>
@@ -9487,7 +9491,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI19" s="94"/>
+      <c r="BI19" s="107"/>
       <c r="BJ19" s="5"/>
       <c r="BK19" s="5"/>
       <c r="BL19" s="5"/>
@@ -9542,7 +9546,7 @@
       </c>
       <c r="G20" s="61"/>
       <c r="H20" s="59"/>
-      <c r="I20" s="126" t="e">
+      <c r="I20" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -9627,7 +9631,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI20" s="94"/>
+      <c r="BI20" s="107"/>
       <c r="BJ20" s="61"/>
       <c r="BK20" s="61"/>
       <c r="BL20" s="61"/>
@@ -9687,7 +9691,7 @@
         <f>_xlfn.XLOOKUP(C21,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I21" s="124">
+      <c r="I21" s="97">
         <f t="shared" si="14"/>
         <v>93</v>
       </c>
@@ -9852,7 +9856,7 @@
         <f t="shared" si="9"/>
         <v>0.25</v>
       </c>
-      <c r="BI21" s="94"/>
+      <c r="BI21" s="107"/>
       <c r="BJ21" s="5"/>
       <c r="BK21" s="5"/>
       <c r="BL21" s="5"/>
@@ -9905,7 +9909,7 @@
       <c r="F22" s="61"/>
       <c r="G22" s="61"/>
       <c r="H22" s="59"/>
-      <c r="I22" s="126" t="e">
+      <c r="I22" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -9990,7 +9994,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI22" s="94"/>
+      <c r="BI22" s="107"/>
       <c r="BJ22" s="61"/>
       <c r="BK22" s="61"/>
       <c r="BL22" s="61"/>
@@ -10045,7 +10049,7 @@
       <c r="F23" s="61"/>
       <c r="G23" s="61"/>
       <c r="H23" s="59"/>
-      <c r="I23" s="126" t="e">
+      <c r="I23" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -10130,7 +10134,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI23" s="94"/>
+      <c r="BI23" s="107"/>
       <c r="BJ23" s="61"/>
       <c r="BK23" s="61"/>
       <c r="BL23" s="61"/>
@@ -10183,7 +10187,7 @@
       <c r="F24" s="61"/>
       <c r="G24" s="61"/>
       <c r="H24" s="59"/>
-      <c r="I24" s="126" t="e">
+      <c r="I24" s="99" t="e">
         <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
@@ -10268,7 +10272,7 @@
         <f t="shared" si="9"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BI24" s="94"/>
+      <c r="BI24" s="107"/>
       <c r="BJ24" s="61"/>
       <c r="BK24" s="61"/>
       <c r="BL24" s="61"/>
@@ -10330,7 +10334,7 @@
         <f>_xlfn.XLOOKUP(C25,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I25" s="124">
+      <c r="I25" s="97">
         <f t="shared" si="14"/>
         <v>64.474999999999994</v>
       </c>
@@ -10495,7 +10499,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI25" s="94"/>
+      <c r="BI25" s="107"/>
       <c r="BJ25" s="5"/>
       <c r="BK25" s="5"/>
       <c r="BL25" s="5"/>
@@ -10557,7 +10561,7 @@
         <f>_xlfn.XLOOKUP(C26,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I26" s="124">
+      <c r="I26" s="97">
         <f t="shared" si="14"/>
         <v>47.5</v>
       </c>
@@ -10722,7 +10726,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI26" s="94"/>
+      <c r="BI26" s="107"/>
       <c r="BJ26" s="7"/>
       <c r="BK26" s="7"/>
       <c r="BL26" s="7"/>
@@ -10786,7 +10790,7 @@
         <f>_xlfn.XLOOKUP(C27,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I27" s="124">
+      <c r="I27" s="97">
         <f t="shared" si="14"/>
         <v>86</v>
       </c>
@@ -10951,7 +10955,7 @@
         <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
-      <c r="BI27" s="94"/>
+      <c r="BI27" s="107"/>
       <c r="BJ27" s="5"/>
       <c r="BK27" s="5"/>
       <c r="BL27" s="5"/>
@@ -11013,7 +11017,7 @@
         <f>_xlfn.XLOOKUP(C28,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I28" s="124">
+      <c r="I28" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -11178,7 +11182,7 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="BI28" s="94"/>
+      <c r="BI28" s="107"/>
       <c r="BJ28" s="7"/>
       <c r="BK28" s="7"/>
       <c r="BL28" s="7"/>
@@ -11240,7 +11244,7 @@
         <f>_xlfn.XLOOKUP(C29,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I29" s="124">
+      <c r="I29" s="97">
         <f t="shared" si="14"/>
         <v>93.699999999999989</v>
       </c>
@@ -11405,7 +11409,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI29" s="94"/>
+      <c r="BI29" s="107"/>
       <c r="BJ29" s="5"/>
       <c r="BK29" s="5"/>
       <c r="BL29" s="5"/>
@@ -11467,7 +11471,7 @@
         <f>_xlfn.XLOOKUP(C30,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I30" s="124">
+      <c r="I30" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -11632,7 +11636,7 @@
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="BI30" s="94"/>
+      <c r="BI30" s="107"/>
       <c r="BJ30" s="7"/>
       <c r="BK30" s="7"/>
       <c r="BL30" s="7"/>
@@ -11702,7 +11706,7 @@
         <f>_xlfn.XLOOKUP(C31,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I31" s="124">
+      <c r="I31" s="97">
         <f t="shared" si="14"/>
         <v>65</v>
       </c>
@@ -11867,7 +11871,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI31" s="94"/>
+      <c r="BI31" s="107"/>
       <c r="BJ31" s="5"/>
       <c r="BK31" s="5"/>
       <c r="BL31" s="5"/>
@@ -11927,7 +11931,7 @@
         <f>_xlfn.XLOOKUP(C32,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I32" s="124">
+      <c r="I32" s="97">
         <f t="shared" si="14"/>
         <v>63.424999999999997</v>
       </c>
@@ -12092,7 +12096,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI32" s="94"/>
+      <c r="BI32" s="107"/>
       <c r="BJ32" s="7"/>
       <c r="BK32" s="7"/>
       <c r="BL32" s="7"/>
@@ -12154,7 +12158,7 @@
         <f>_xlfn.XLOOKUP(C33,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I33" s="124">
+      <c r="I33" s="97">
         <f t="shared" si="14"/>
         <v>32.519999999999996</v>
       </c>
@@ -12319,7 +12323,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI33" s="94"/>
+      <c r="BI33" s="107"/>
       <c r="BJ33" s="5"/>
       <c r="BK33" s="5"/>
       <c r="BL33" s="5"/>
@@ -12383,7 +12387,7 @@
         <f>_xlfn.XLOOKUP(C34,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I34" s="124">
+      <c r="I34" s="97">
         <f t="shared" si="14"/>
         <v>90.759999999999991</v>
       </c>
@@ -12548,7 +12552,7 @@
         <f t="shared" si="9"/>
         <v>0.2</v>
       </c>
-      <c r="BI34" s="94"/>
+      <c r="BI34" s="107"/>
       <c r="BJ34" s="7"/>
       <c r="BK34" s="7"/>
       <c r="BL34" s="7"/>
@@ -12610,7 +12614,7 @@
         <f>_xlfn.XLOOKUP(C35,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I35" s="124">
+      <c r="I35" s="97">
         <f t="shared" si="14"/>
         <v>97.899999999999991</v>
       </c>
@@ -12775,7 +12779,7 @@
         <f t="shared" si="9"/>
         <v>0.6</v>
       </c>
-      <c r="BI35" s="94"/>
+      <c r="BI35" s="107"/>
       <c r="BJ35" s="5">
         <v>0.5</v>
       </c>
@@ -12845,7 +12849,7 @@
         <f>_xlfn.XLOOKUP(C36,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>0.9285714285714286</v>
       </c>
-      <c r="I36" s="124">
+      <c r="I36" s="97">
         <f t="shared" si="14"/>
         <v>85.005714285714291</v>
       </c>
@@ -13010,7 +13014,7 @@
         <f t="shared" si="9"/>
         <v>0.05</v>
       </c>
-      <c r="BI36" s="94"/>
+      <c r="BI36" s="107"/>
       <c r="BJ36" s="7"/>
       <c r="BK36" s="7"/>
       <c r="BL36" s="7"/>
@@ -13072,7 +13076,7 @@
         <f>_xlfn.XLOOKUP(C37,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I37" s="124">
+      <c r="I37" s="97">
         <f t="shared" si="14"/>
         <v>96.5</v>
       </c>
@@ -13239,7 +13243,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI37" s="94"/>
+      <c r="BI37" s="107"/>
       <c r="BJ37" s="5"/>
       <c r="BK37" s="5"/>
       <c r="BL37" s="5"/>
@@ -13301,7 +13305,7 @@
         <f>_xlfn.XLOOKUP(C38,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I38" s="124">
+      <c r="I38" s="97">
         <f t="shared" si="14"/>
         <v>68.674999999999997</v>
       </c>
@@ -13466,7 +13470,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI38" s="94"/>
+      <c r="BI38" s="107"/>
       <c r="BJ38" s="7"/>
       <c r="BK38" s="7"/>
       <c r="BL38" s="7"/>
@@ -13528,7 +13532,7 @@
         <f>_xlfn.XLOOKUP(C39,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="I39" s="124">
+      <c r="I39" s="97">
         <f t="shared" si="14"/>
         <v>100</v>
       </c>
@@ -13693,7 +13697,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="BI39" s="95"/>
+      <c r="BI39" s="108"/>
       <c r="BJ39" s="5"/>
       <c r="BK39" s="5"/>
       <c r="BL39" s="5"/>
@@ -13745,7 +13749,7 @@
         <f>_xlfn.XLOOKUP(C40,'[1]5A_CD'!$C:$C,'[1]5A_CD'!$J:$J,"")</f>
         <v>0</v>
       </c>
-      <c r="I40" s="124">
+      <c r="I40" s="97">
         <f t="shared" si="14"/>
         <v>34</v>
       </c>
@@ -14062,14 +14066,14 @@
       <c r="G3" s="16">
         <v>95</v>
       </c>
-      <c r="H3" s="117">
+      <c r="H3" s="90">
         <f>_xlfn.XLOOKUP(C3,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="I3" s="5">
         <v>1</v>
       </c>
-      <c r="J3" s="120">
+      <c r="J3" s="93">
         <f>G3*0.7+H3*20+I3*10</f>
         <v>96.5</v>
       </c>
@@ -14122,14 +14126,14 @@
       <c r="G4" s="16">
         <v>97.5</v>
       </c>
-      <c r="H4" s="117">
+      <c r="H4" s="90">
         <f>_xlfn.XLOOKUP(C4,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.91304347826086951</v>
       </c>
       <c r="I4" s="7">
         <v>1</v>
       </c>
-      <c r="J4" s="120">
+      <c r="J4" s="93">
         <f t="shared" ref="J4:J36" si="0">G4*0.7+H4*20+I4*10</f>
         <v>96.510869565217391</v>
       </c>
@@ -14182,14 +14186,14 @@
       <c r="G5" s="16">
         <v>50</v>
       </c>
-      <c r="H5" s="117">
+      <c r="H5" s="90">
         <f>_xlfn.XLOOKUP(C5,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.91304347826086951</v>
       </c>
       <c r="I5" s="5">
         <v>1</v>
       </c>
-      <c r="J5" s="120">
+      <c r="J5" s="93">
         <f t="shared" si="0"/>
         <v>63.260869565217391</v>
       </c>
@@ -14240,9 +14244,9 @@
       <c r="E6" s="61"/>
       <c r="F6" s="61"/>
       <c r="G6" s="61"/>
-      <c r="H6" s="117"/>
+      <c r="H6" s="90"/>
       <c r="I6" s="61"/>
-      <c r="J6" s="120">
+      <c r="J6" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14293,9 +14297,9 @@
       <c r="E7" s="61"/>
       <c r="F7" s="61"/>
       <c r="G7" s="61"/>
-      <c r="H7" s="117"/>
+      <c r="H7" s="90"/>
       <c r="I7" s="61"/>
-      <c r="J7" s="120">
+      <c r="J7" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14352,14 +14356,14 @@
       <c r="G8" s="16">
         <v>70</v>
       </c>
-      <c r="H8" s="117">
+      <c r="H8" s="90">
         <f>_xlfn.XLOOKUP(C8,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.72727272727272729</v>
       </c>
       <c r="I8" s="7">
         <v>1</v>
       </c>
-      <c r="J8" s="120">
+      <c r="J8" s="93">
         <f t="shared" si="0"/>
         <v>73.545454545454547</v>
       </c>
@@ -14410,9 +14414,9 @@
       <c r="E9" s="61"/>
       <c r="F9" s="61"/>
       <c r="G9" s="61"/>
-      <c r="H9" s="117"/>
+      <c r="H9" s="90"/>
       <c r="I9" s="61"/>
-      <c r="J9" s="120">
+      <c r="J9" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14463,9 +14467,9 @@
       <c r="E10" s="61"/>
       <c r="F10" s="61"/>
       <c r="G10" s="61"/>
-      <c r="H10" s="117"/>
+      <c r="H10" s="90"/>
       <c r="I10" s="61"/>
-      <c r="J10" s="120">
+      <c r="J10" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14522,14 +14526,14 @@
       <c r="G11" s="73">
         <v>100</v>
       </c>
-      <c r="H11" s="117">
+      <c r="H11" s="90">
         <f>_xlfn.XLOOKUP(C11,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.95652173913043481</v>
       </c>
       <c r="I11" s="73">
         <v>1</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="93">
         <f t="shared" si="0"/>
         <v>99.130434782608688</v>
       </c>
@@ -14584,9 +14588,9 @@
         <v>1</v>
       </c>
       <c r="G12" s="61"/>
-      <c r="H12" s="117"/>
+      <c r="H12" s="90"/>
       <c r="I12" s="61"/>
-      <c r="J12" s="120">
+      <c r="J12" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14639,14 +14643,14 @@
       <c r="G13" s="16">
         <v>90</v>
       </c>
-      <c r="H13" s="117">
+      <c r="H13" s="90">
         <f>_xlfn.XLOOKUP(C13,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="I13" s="5">
         <v>1</v>
       </c>
-      <c r="J13" s="120">
+      <c r="J13" s="93">
         <f t="shared" si="0"/>
         <v>73.869565217391298</v>
       </c>
@@ -14688,7 +14692,7 @@
       <c r="B14" s="7">
         <v>1</v>
       </c>
-      <c r="C14" s="116" t="s">
+      <c r="C14" s="89" t="s">
         <v>198</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -14704,14 +14708,14 @@
         <f>70+10</f>
         <v>80</v>
       </c>
-      <c r="H14" s="117">
+      <c r="H14" s="90">
         <f>_xlfn.XLOOKUP(C14,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="I14" s="7">
         <v>1</v>
       </c>
-      <c r="J14" s="120">
+      <c r="J14" s="93">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
@@ -14762,9 +14766,9 @@
       <c r="E15" s="61"/>
       <c r="F15" s="61"/>
       <c r="G15" s="61"/>
-      <c r="H15" s="117"/>
+      <c r="H15" s="90"/>
       <c r="I15" s="61"/>
-      <c r="J15" s="120">
+      <c r="J15" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -14821,14 +14825,14 @@
       <c r="G16" s="16">
         <v>65</v>
       </c>
-      <c r="H16" s="117">
+      <c r="H16" s="90">
         <f>_xlfn.XLOOKUP(C16,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.86363636363636365</v>
       </c>
       <c r="I16" s="7">
         <v>1</v>
       </c>
-      <c r="J16" s="120">
+      <c r="J16" s="93">
         <f t="shared" si="0"/>
         <v>72.77272727272728</v>
       </c>
@@ -14881,14 +14885,14 @@
       <c r="G17" s="16">
         <v>100</v>
       </c>
-      <c r="H17" s="117">
+      <c r="H17" s="90">
         <f>_xlfn.XLOOKUP(C17,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.95652173913043481</v>
       </c>
       <c r="I17" s="5">
         <v>1</v>
       </c>
-      <c r="J17" s="120">
+      <c r="J17" s="93">
         <f t="shared" si="0"/>
         <v>99.130434782608688</v>
       </c>
@@ -14930,7 +14934,7 @@
       <c r="B18" s="7">
         <v>1</v>
       </c>
-      <c r="C18" s="116" t="s">
+      <c r="C18" s="89" t="s">
         <v>189</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -14943,14 +14947,14 @@
       <c r="G18" s="16">
         <v>100</v>
       </c>
-      <c r="H18" s="117">
+      <c r="H18" s="90">
         <f>_xlfn.XLOOKUP(C18,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.91304347826086951</v>
       </c>
       <c r="I18" s="7">
         <v>1</v>
       </c>
-      <c r="J18" s="120">
+      <c r="J18" s="93">
         <f t="shared" si="0"/>
         <v>98.260869565217391</v>
       </c>
@@ -15003,14 +15007,14 @@
       <c r="G19" s="16">
         <v>100</v>
       </c>
-      <c r="H19" s="117">
+      <c r="H19" s="90">
         <f>_xlfn.XLOOKUP(C19,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.90909090909090906</v>
       </c>
       <c r="I19" s="5">
         <v>1</v>
       </c>
-      <c r="J19" s="120">
+      <c r="J19" s="93">
         <f t="shared" si="0"/>
         <v>98.181818181818187</v>
       </c>
@@ -15061,9 +15065,9 @@
       <c r="E20" s="61"/>
       <c r="F20" s="61"/>
       <c r="G20" s="61"/>
-      <c r="H20" s="117"/>
+      <c r="H20" s="90"/>
       <c r="I20" s="61"/>
-      <c r="J20" s="120">
+      <c r="J20" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15116,14 +15120,14 @@
       <c r="G21" s="16">
         <v>0</v>
       </c>
-      <c r="H21" s="117">
+      <c r="H21" s="90">
         <f>_xlfn.XLOOKUP(C21,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.95652173913043481</v>
       </c>
       <c r="I21" s="5">
         <v>1</v>
       </c>
-      <c r="J21" s="120">
+      <c r="J21" s="93">
         <f t="shared" si="0"/>
         <v>29.130434782608695</v>
       </c>
@@ -15176,14 +15180,14 @@
       <c r="G22" s="16">
         <v>25</v>
       </c>
-      <c r="H22" s="117">
+      <c r="H22" s="90">
         <f>_xlfn.XLOOKUP(C22,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="I22" s="7">
         <v>1</v>
       </c>
-      <c r="J22" s="120">
+      <c r="J22" s="93">
         <f t="shared" si="0"/>
         <v>47.5</v>
       </c>
@@ -15238,14 +15242,14 @@
       <c r="G23" s="16">
         <v>100</v>
       </c>
-      <c r="H23" s="117">
+      <c r="H23" s="90">
         <f>_xlfn.XLOOKUP(C23,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.73913043478260865</v>
       </c>
       <c r="I23" s="5">
         <v>1</v>
       </c>
-      <c r="J23" s="120">
+      <c r="J23" s="93">
         <f t="shared" si="0"/>
         <v>94.782608695652172</v>
       </c>
@@ -15298,14 +15302,14 @@
       <c r="G24" s="16">
         <v>0</v>
       </c>
-      <c r="H24" s="117">
+      <c r="H24" s="90">
         <f>_xlfn.XLOOKUP(C24,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.82608695652173914</v>
       </c>
       <c r="I24" s="7">
         <v>1</v>
       </c>
-      <c r="J24" s="120">
+      <c r="J24" s="93">
         <f t="shared" si="0"/>
         <v>26.521739130434781</v>
       </c>
@@ -15358,14 +15362,14 @@
       <c r="G25" s="16">
         <v>0</v>
       </c>
-      <c r="H25" s="117">
+      <c r="H25" s="90">
         <f>_xlfn.XLOOKUP(C25,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="I25" s="5">
         <v>1</v>
       </c>
-      <c r="J25" s="120">
+      <c r="J25" s="93">
         <f t="shared" si="0"/>
         <v>10.869565217391305</v>
       </c>
@@ -15420,14 +15424,14 @@
       <c r="G26" s="16">
         <v>47.5</v>
       </c>
-      <c r="H26" s="117">
+      <c r="H26" s="90">
         <f>_xlfn.XLOOKUP(C26,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.91304347826086951</v>
       </c>
       <c r="I26" s="7">
         <v>1</v>
       </c>
-      <c r="J26" s="120">
+      <c r="J26" s="93">
         <f t="shared" si="0"/>
         <v>61.510869565217391</v>
       </c>
@@ -15480,14 +15484,14 @@
       <c r="G27" s="16">
         <v>85</v>
       </c>
-      <c r="H27" s="117">
+      <c r="H27" s="90">
         <f>_xlfn.XLOOKUP(C27,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="I27" s="5">
         <v>1</v>
       </c>
-      <c r="J27" s="120">
+      <c r="J27" s="93">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
@@ -15540,14 +15544,14 @@
       <c r="G28" s="16">
         <v>100</v>
       </c>
-      <c r="H28" s="117">
+      <c r="H28" s="90">
         <f>_xlfn.XLOOKUP(C28,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.82608695652173914</v>
       </c>
       <c r="I28" s="7">
         <v>1</v>
       </c>
-      <c r="J28" s="120">
+      <c r="J28" s="93">
         <f t="shared" si="0"/>
         <v>96.521739130434781</v>
       </c>
@@ -15604,14 +15608,14 @@
       <c r="G29" s="16">
         <v>100</v>
       </c>
-      <c r="H29" s="117">
+      <c r="H29" s="90">
         <f>_xlfn.XLOOKUP(C29,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.95652173913043481</v>
       </c>
       <c r="I29" s="5">
         <v>1</v>
       </c>
-      <c r="J29" s="120">
+      <c r="J29" s="93">
         <f t="shared" si="0"/>
         <v>99.130434782608688</v>
       </c>
@@ -15662,9 +15666,9 @@
       <c r="E30" s="61"/>
       <c r="F30" s="61"/>
       <c r="G30" s="61"/>
-      <c r="H30" s="117"/>
+      <c r="H30" s="90"/>
       <c r="I30" s="61"/>
-      <c r="J30" s="120">
+      <c r="J30" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15715,9 +15719,9 @@
       <c r="E31" s="61"/>
       <c r="F31" s="61"/>
       <c r="G31" s="61"/>
-      <c r="H31" s="117"/>
+      <c r="H31" s="90"/>
       <c r="I31" s="61"/>
-      <c r="J31" s="120">
+      <c r="J31" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15768,9 +15772,9 @@
       <c r="E32" s="61"/>
       <c r="F32" s="61"/>
       <c r="G32" s="61"/>
-      <c r="H32" s="117"/>
+      <c r="H32" s="90"/>
       <c r="I32" s="61"/>
-      <c r="J32" s="120">
+      <c r="J32" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15823,14 +15827,14 @@
       <c r="G33" s="16">
         <v>25</v>
       </c>
-      <c r="H33" s="117">
+      <c r="H33" s="90">
         <f>_xlfn.XLOOKUP(C33,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.86956521739130432</v>
       </c>
       <c r="I33" s="5">
         <v>1</v>
       </c>
-      <c r="J33" s="120">
+      <c r="J33" s="93">
         <f t="shared" si="0"/>
         <v>44.891304347826086</v>
       </c>
@@ -15883,14 +15887,14 @@
       <c r="G34" s="16">
         <v>0</v>
       </c>
-      <c r="H34" s="117">
+      <c r="H34" s="90">
         <f>_xlfn.XLOOKUP(C34,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.60869565217391308</v>
       </c>
       <c r="I34" s="7">
         <v>1</v>
       </c>
-      <c r="J34" s="120">
+      <c r="J34" s="93">
         <f t="shared" si="0"/>
         <v>22.173913043478262</v>
       </c>
@@ -15941,9 +15945,9 @@
       <c r="E35" s="61"/>
       <c r="F35" s="61"/>
       <c r="G35" s="61"/>
-      <c r="H35" s="117"/>
+      <c r="H35" s="90"/>
       <c r="I35" s="61"/>
-      <c r="J35" s="120">
+      <c r="J35" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -15996,14 +16000,14 @@
       <c r="G36" s="16">
         <v>15</v>
       </c>
-      <c r="H36" s="117">
+      <c r="H36" s="90">
         <f>_xlfn.XLOOKUP(C36,[1]M08_CI!$C:$C,[1]M08_CI!$I:$I,"")</f>
         <v>0.91304347826086951</v>
       </c>
       <c r="I36" s="7">
         <v>1</v>
       </c>
-      <c r="J36" s="120">
+      <c r="J36" s="93">
         <f t="shared" si="0"/>
         <v>38.760869565217391</v>
       </c>
@@ -16155,7 +16159,7 @@
       <c r="D2" s="72"/>
       <c r="E2" s="16"/>
       <c r="F2" s="67"/>
-      <c r="G2" s="120">
+      <c r="G2" s="93">
         <f>D2*0.7+E2*20+F2*10</f>
         <v>0</v>
       </c>
@@ -16209,7 +16213,7 @@
       <c r="F3" s="11">
         <v>1</v>
       </c>
-      <c r="G3" s="120">
+      <c r="G3" s="93">
         <f t="shared" ref="G3:G35" si="0">D3*0.7+E3*20+F3*10</f>
         <v>44</v>
       </c>
@@ -16256,7 +16260,7 @@
       <c r="D4" s="72"/>
       <c r="E4" s="16"/>
       <c r="F4" s="67"/>
-      <c r="G4" s="120">
+      <c r="G4" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16310,7 +16314,7 @@
       <c r="F5" s="11">
         <v>1</v>
       </c>
-      <c r="G5" s="120">
+      <c r="G5" s="93">
         <f t="shared" si="0"/>
         <v>77.666666666666671</v>
       </c>
@@ -16364,7 +16368,7 @@
       <c r="F6" s="10">
         <v>1</v>
       </c>
-      <c r="G6" s="120">
+      <c r="G6" s="93">
         <f t="shared" si="0"/>
         <v>40.5</v>
       </c>
@@ -16418,7 +16422,7 @@
       <c r="F7" s="11">
         <v>1</v>
       </c>
-      <c r="G7" s="120">
+      <c r="G7" s="93">
         <f t="shared" si="0"/>
         <v>42.666666666666671</v>
       </c>
@@ -16472,7 +16476,7 @@
       <c r="F8" s="10">
         <v>1</v>
       </c>
-      <c r="G8" s="120">
+      <c r="G8" s="93">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -16526,7 +16530,7 @@
       <c r="F9" s="11">
         <v>1</v>
       </c>
-      <c r="G9" s="120">
+      <c r="G9" s="93">
         <f t="shared" si="0"/>
         <v>92.083333333333343</v>
       </c>
@@ -16580,7 +16584,7 @@
       <c r="F10" s="10">
         <v>1</v>
       </c>
-      <c r="G10" s="120">
+      <c r="G10" s="93">
         <f t="shared" si="0"/>
         <v>88.625</v>
       </c>
@@ -16634,7 +16638,7 @@
       <c r="F11" s="7">
         <v>1</v>
       </c>
-      <c r="G11" s="120">
+      <c r="G11" s="93">
         <f t="shared" si="0"/>
         <v>69.333333333333343</v>
       </c>
@@ -16681,7 +16685,7 @@
       <c r="D12" s="72"/>
       <c r="E12" s="16"/>
       <c r="F12" s="67"/>
-      <c r="G12" s="120">
+      <c r="G12" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16735,7 +16739,7 @@
       <c r="F13" s="11">
         <v>1</v>
       </c>
-      <c r="G13" s="120">
+      <c r="G13" s="93">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -16789,7 +16793,7 @@
       <c r="F14" s="10">
         <v>1</v>
       </c>
-      <c r="G14" s="120">
+      <c r="G14" s="93">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -16836,7 +16840,7 @@
       <c r="D15" s="72"/>
       <c r="E15" s="16"/>
       <c r="F15" s="67"/>
-      <c r="G15" s="120">
+      <c r="G15" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -16890,7 +16894,7 @@
       <c r="F16" s="10">
         <v>1</v>
       </c>
-      <c r="G16" s="120">
+      <c r="G16" s="93">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -16944,7 +16948,7 @@
       <c r="F17" s="11">
         <v>1</v>
       </c>
-      <c r="G17" s="120">
+      <c r="G17" s="93">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -16998,7 +17002,7 @@
       <c r="F18" s="5">
         <v>1</v>
       </c>
-      <c r="G18" s="120">
+      <c r="G18" s="93">
         <f t="shared" si="0"/>
         <v>68.5</v>
       </c>
@@ -17052,7 +17056,7 @@
       <c r="F19" s="11">
         <v>1</v>
       </c>
-      <c r="G19" s="120">
+      <c r="G19" s="93">
         <f t="shared" si="0"/>
         <v>46.166666666666671</v>
       </c>
@@ -17106,7 +17110,7 @@
       <c r="F20" s="10">
         <v>1</v>
       </c>
-      <c r="G20" s="120">
+      <c r="G20" s="93">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -17160,7 +17164,7 @@
       <c r="F21" s="11">
         <v>1</v>
       </c>
-      <c r="G21" s="120">
+      <c r="G21" s="93">
         <f t="shared" si="0"/>
         <v>75.5</v>
       </c>
@@ -17214,7 +17218,7 @@
       <c r="F22" s="10">
         <v>1</v>
       </c>
-      <c r="G22" s="120">
+      <c r="G22" s="93">
         <f t="shared" si="0"/>
         <v>40.5</v>
       </c>
@@ -17268,7 +17272,7 @@
       <c r="F23" s="11">
         <v>1</v>
       </c>
-      <c r="G23" s="120">
+      <c r="G23" s="93">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -17315,7 +17319,7 @@
       <c r="D24" s="72"/>
       <c r="E24" s="16"/>
       <c r="F24" s="67"/>
-      <c r="G24" s="120">
+      <c r="G24" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -17369,7 +17373,7 @@
       <c r="F25" s="11">
         <v>1</v>
       </c>
-      <c r="G25" s="120">
+      <c r="G25" s="93">
         <f t="shared" si="0"/>
         <v>89.5</v>
       </c>
@@ -17423,7 +17427,7 @@
       <c r="F26" s="10">
         <v>1</v>
       </c>
-      <c r="G26" s="120">
+      <c r="G26" s="93">
         <f t="shared" si="0"/>
         <v>93.833333333333343</v>
       </c>
@@ -17470,7 +17474,7 @@
       <c r="D27" s="72"/>
       <c r="E27" s="16"/>
       <c r="F27" s="67"/>
-      <c r="G27" s="120">
+      <c r="G27" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -17524,7 +17528,7 @@
       <c r="F28" s="5">
         <v>1</v>
       </c>
-      <c r="G28" s="120">
+      <c r="G28" s="93">
         <f t="shared" si="0"/>
         <v>59.116666666666667</v>
       </c>
@@ -17578,7 +17582,7 @@
       <c r="F29" s="11">
         <v>1</v>
       </c>
-      <c r="G29" s="120">
+      <c r="G29" s="93">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -17632,7 +17636,7 @@
       <c r="F30" s="10">
         <v>1</v>
       </c>
-      <c r="G30" s="120">
+      <c r="G30" s="93">
         <f t="shared" si="0"/>
         <v>39.166666666666671</v>
       </c>
@@ -17679,7 +17683,7 @@
       <c r="D31" s="72"/>
       <c r="E31" s="16"/>
       <c r="F31" s="61"/>
-      <c r="G31" s="120">
+      <c r="G31" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -17733,7 +17737,7 @@
       <c r="F32" s="10">
         <v>1</v>
       </c>
-      <c r="G32" s="120">
+      <c r="G32" s="93">
         <f t="shared" si="0"/>
         <v>18.333333333333336</v>
       </c>
@@ -17780,7 +17784,7 @@
       <c r="D33" s="72"/>
       <c r="E33" s="16"/>
       <c r="F33" s="61"/>
-      <c r="G33" s="120">
+      <c r="G33" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -17834,7 +17838,7 @@
       <c r="F34" s="5">
         <v>1</v>
       </c>
-      <c r="G34" s="120">
+      <c r="G34" s="93">
         <f t="shared" si="0"/>
         <v>47.833333333333329</v>
       </c>
@@ -17888,7 +17892,7 @@
       <c r="F35" s="7">
         <v>1</v>
       </c>
-      <c r="G35" s="120">
+      <c r="G35" s="93">
         <f t="shared" si="0"/>
         <v>24.285714285714285</v>
       </c>
@@ -18030,7 +18034,7 @@
       <c r="I2" s="16">
         <v>1</v>
       </c>
-      <c r="J2" s="120">
+      <c r="J2" s="93">
         <f>G2*0.7+H2*20+I2*10</f>
         <v>90.486363636363635</v>
       </c>
@@ -18083,8 +18087,8 @@
       <c r="G3" s="61"/>
       <c r="H3" s="16"/>
       <c r="I3" s="16"/>
-      <c r="J3" s="120">
-        <f t="shared" ref="J3:J33" si="0">G3*0.7+H3*20+I3*10</f>
+      <c r="J3" s="93">
+        <f t="shared" ref="J3:J32" si="0">G3*0.7+H3*20+I3*10</f>
         <v>0</v>
       </c>
       <c r="K3" s="61"/>
@@ -18147,7 +18151,7 @@
       <c r="I4" s="16">
         <v>1</v>
       </c>
-      <c r="J4" s="120">
+      <c r="J4" s="93">
         <f t="shared" si="0"/>
         <v>56.304347826086953</v>
       </c>
@@ -18211,7 +18215,7 @@
       <c r="I5" s="16">
         <v>1</v>
       </c>
-      <c r="J5" s="120">
+      <c r="J5" s="93">
         <f t="shared" si="0"/>
         <v>82.645454545454541</v>
       </c>
@@ -18273,7 +18277,7 @@
       <c r="I6" s="16">
         <v>1</v>
       </c>
-      <c r="J6" s="120">
+      <c r="J6" s="93">
         <f t="shared" si="0"/>
         <v>98.260869565217391</v>
       </c>
@@ -18326,7 +18330,7 @@
       <c r="G7" s="61"/>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
-      <c r="J7" s="120">
+      <c r="J7" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -18390,7 +18394,7 @@
       <c r="I8" s="16">
         <v>1</v>
       </c>
-      <c r="J8" s="120">
+      <c r="J8" s="93">
         <f t="shared" si="0"/>
         <v>94.782608695652172</v>
       </c>
@@ -18445,7 +18449,7 @@
       <c r="G9" s="61"/>
       <c r="H9" s="16"/>
       <c r="I9" s="16"/>
-      <c r="J9" s="120">
+      <c r="J9" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -18505,7 +18509,7 @@
       <c r="I10" s="16">
         <v>1</v>
       </c>
-      <c r="J10" s="120">
+      <c r="J10" s="93">
         <f t="shared" si="0"/>
         <v>37.913043478260867</v>
       </c>
@@ -18567,7 +18571,7 @@
       <c r="I11" s="16">
         <v>1</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="93">
         <f t="shared" si="0"/>
         <v>93.913043478260875</v>
       </c>
@@ -18627,7 +18631,7 @@
       <c r="I12" s="16">
         <v>1</v>
       </c>
-      <c r="J12" s="120">
+      <c r="J12" s="93">
         <f t="shared" si="0"/>
         <v>53.045454545454547</v>
       </c>
@@ -18680,7 +18684,7 @@
       <c r="G13" s="61"/>
       <c r="H13" s="16"/>
       <c r="I13" s="16"/>
-      <c r="J13" s="120">
+      <c r="J13" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -18738,7 +18742,7 @@
       <c r="I14" s="16">
         <v>1</v>
       </c>
-      <c r="J14" s="120">
+      <c r="J14" s="93">
         <f t="shared" si="0"/>
         <v>15.217391304347826</v>
       </c>
@@ -18791,7 +18795,7 @@
       <c r="G15" s="61"/>
       <c r="H15" s="16"/>
       <c r="I15" s="16"/>
-      <c r="J15" s="120">
+      <c r="J15" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -18855,7 +18859,7 @@
       <c r="I16" s="16">
         <v>1</v>
       </c>
-      <c r="J16" s="120">
+      <c r="J16" s="93">
         <f t="shared" si="0"/>
         <v>43.152173913043477</v>
       </c>
@@ -18915,7 +18919,7 @@
       <c r="I17" s="16">
         <v>1</v>
       </c>
-      <c r="J17" s="120">
+      <c r="J17" s="93">
         <f t="shared" si="0"/>
         <v>85.217391304347828</v>
       </c>
@@ -18979,7 +18983,7 @@
       <c r="I18" s="16">
         <v>1</v>
       </c>
-      <c r="J18" s="120">
+      <c r="J18" s="93">
         <f t="shared" si="0"/>
         <v>67.65217391304347</v>
       </c>
@@ -19043,7 +19047,7 @@
       <c r="I19" s="16">
         <v>1</v>
       </c>
-      <c r="J19" s="120">
+      <c r="J19" s="93">
         <f t="shared" si="0"/>
         <v>47.521739130434781</v>
       </c>
@@ -19107,7 +19111,7 @@
       <c r="I20" s="16">
         <v>1</v>
       </c>
-      <c r="J20" s="120">
+      <c r="J20" s="93">
         <f t="shared" si="0"/>
         <v>46.652173913043477</v>
       </c>
@@ -19171,7 +19175,7 @@
       <c r="I21" s="16">
         <v>1</v>
       </c>
-      <c r="J21" s="120">
+      <c r="J21" s="93">
         <f t="shared" si="0"/>
         <v>95.652173913043484</v>
       </c>
@@ -19228,7 +19232,7 @@
       <c r="G22" s="61"/>
       <c r="H22" s="16"/>
       <c r="I22" s="16"/>
-      <c r="J22" s="120">
+      <c r="J22" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19292,7 +19296,7 @@
       <c r="I23" s="16">
         <v>1</v>
       </c>
-      <c r="J23" s="120">
+      <c r="J23" s="93">
         <f t="shared" si="0"/>
         <v>61.521739130434781</v>
       </c>
@@ -19356,7 +19360,7 @@
       <c r="I24" s="16">
         <v>1</v>
       </c>
-      <c r="J24" s="120">
+      <c r="J24" s="93">
         <f t="shared" si="0"/>
         <v>95.652173913043484</v>
       </c>
@@ -19420,7 +19424,7 @@
       <c r="I25" s="16">
         <v>1</v>
       </c>
-      <c r="J25" s="120">
+      <c r="J25" s="93">
         <f t="shared" si="0"/>
         <v>61.554347826086953</v>
       </c>
@@ -19473,7 +19477,7 @@
       <c r="G26" s="61"/>
       <c r="H26" s="16"/>
       <c r="I26" s="16"/>
-      <c r="J26" s="120">
+      <c r="J26" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19528,7 +19532,7 @@
       <c r="G27" s="61"/>
       <c r="H27" s="16"/>
       <c r="I27" s="16"/>
-      <c r="J27" s="120">
+      <c r="J27" s="93">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -19590,7 +19594,7 @@
       <c r="I28" s="16">
         <v>1</v>
       </c>
-      <c r="J28" s="120">
+      <c r="J28" s="93">
         <f t="shared" si="0"/>
         <v>60.652173913043477</v>
       </c>
@@ -19652,7 +19656,7 @@
       <c r="I29" s="16">
         <v>1</v>
       </c>
-      <c r="J29" s="120">
+      <c r="J29" s="93">
         <f t="shared" si="0"/>
         <v>15.217391304347826</v>
       </c>
@@ -19716,7 +19720,7 @@
       <c r="I30" s="16">
         <v>1</v>
       </c>
-      <c r="J30" s="120">
+      <c r="J30" s="93">
         <f t="shared" si="0"/>
         <v>50.152173913043477</v>
       </c>
@@ -19780,7 +19784,7 @@
       <c r="I31" s="16">
         <v>1</v>
       </c>
-      <c r="J31" s="120">
+      <c r="J31" s="93">
         <f t="shared" si="0"/>
         <v>95.652173913043484</v>
       </c>
@@ -19844,7 +19848,7 @@
       <c r="I32" s="16">
         <v>1</v>
       </c>
-      <c r="J32" s="120">
+      <c r="J32" s="93">
         <f t="shared" si="0"/>
         <v>62.817391304347822</v>
       </c>
@@ -19880,7 +19884,7 @@
       <c r="AN32" s="5"/>
     </row>
     <row r="33" spans="3:10" s="70" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C33" s="115" t="s">
+      <c r="C33" s="88" t="s">
         <v>736</v>
       </c>
       <c r="G33" s="61"/>
@@ -19888,8 +19892,8 @@
         <f>_xlfn.XLOOKUP(C33,[1]M09_AL!$C:$C,[1]M09_AL!$H:$H,"")</f>
         <v/>
       </c>
-      <c r="I33" s="114"/>
-      <c r="J33" s="120"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="93"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19985,11 +19989,11 @@
       <c r="C1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="96" t="s">
+      <c r="L1" s="114" t="s">
         <v>751</v>
       </c>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
       <c r="O1" s="36"/>
       <c r="P1" s="36"/>
       <c r="Q1" s="29"/>
@@ -20014,7 +20018,7 @@
       <c r="BE1" s="25"/>
       <c r="BF1" s="25"/>
       <c r="BG1" s="9"/>
-      <c r="BH1" s="91" t="s">
+      <c r="BH1" s="104" t="s">
         <v>769</v>
       </c>
       <c r="BL1" s="25"/>
@@ -20048,107 +20052,107 @@
       <c r="G2" s="9"/>
       <c r="H2" s="52"/>
       <c r="I2" s="52"/>
-      <c r="J2" s="89" t="s">
+      <c r="J2" s="102" t="s">
         <v>758</v>
       </c>
       <c r="K2" s="36"/>
-      <c r="L2" s="98" t="s">
+      <c r="L2" s="109" t="s">
         <v>759</v>
       </c>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="99"/>
-      <c r="P2" s="99"/>
-      <c r="Q2" s="100"/>
-      <c r="R2" s="101" t="s">
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="112" t="s">
         <v>760</v>
       </c>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="99"/>
-      <c r="W2" s="102"/>
-      <c r="X2" s="98" t="s">
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="110"/>
+      <c r="V2" s="110"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="109" t="s">
         <v>761</v>
       </c>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="99"/>
-      <c r="AB2" s="99"/>
-      <c r="AC2" s="99"/>
-      <c r="AD2" s="101" t="s">
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
+      <c r="AA2" s="110"/>
+      <c r="AB2" s="110"/>
+      <c r="AC2" s="110"/>
+      <c r="AD2" s="112" t="s">
         <v>762</v>
       </c>
-      <c r="AE2" s="99"/>
-      <c r="AF2" s="99"/>
-      <c r="AG2" s="99"/>
-      <c r="AH2" s="99"/>
-      <c r="AI2" s="102"/>
-      <c r="AJ2" s="88" t="s">
+      <c r="AE2" s="110"/>
+      <c r="AF2" s="110"/>
+      <c r="AG2" s="110"/>
+      <c r="AH2" s="110"/>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="101" t="s">
         <v>765</v>
       </c>
-      <c r="AK2" s="88"/>
-      <c r="AL2" s="88"/>
-      <c r="AM2" s="88"/>
-      <c r="AN2" s="88"/>
-      <c r="AO2" s="88"/>
-      <c r="AP2" s="87" t="s">
+      <c r="AK2" s="101"/>
+      <c r="AL2" s="101"/>
+      <c r="AM2" s="101"/>
+      <c r="AN2" s="101"/>
+      <c r="AO2" s="101"/>
+      <c r="AP2" s="100" t="s">
         <v>766</v>
       </c>
-      <c r="AQ2" s="88"/>
-      <c r="AR2" s="88"/>
-      <c r="AS2" s="88"/>
-      <c r="AT2" s="88"/>
-      <c r="AU2" s="88"/>
-      <c r="AV2" s="87" t="s">
+      <c r="AQ2" s="101"/>
+      <c r="AR2" s="101"/>
+      <c r="AS2" s="101"/>
+      <c r="AT2" s="101"/>
+      <c r="AU2" s="101"/>
+      <c r="AV2" s="100" t="s">
         <v>767</v>
       </c>
-      <c r="AW2" s="88"/>
-      <c r="AX2" s="88"/>
-      <c r="AY2" s="88"/>
-      <c r="AZ2" s="88"/>
-      <c r="BA2" s="88"/>
-      <c r="BB2" s="87" t="s">
+      <c r="AW2" s="101"/>
+      <c r="AX2" s="101"/>
+      <c r="AY2" s="101"/>
+      <c r="AZ2" s="101"/>
+      <c r="BA2" s="101"/>
+      <c r="BB2" s="100" t="s">
         <v>768</v>
       </c>
-      <c r="BC2" s="88"/>
-      <c r="BD2" s="88"/>
-      <c r="BE2" s="88"/>
-      <c r="BF2" s="88"/>
-      <c r="BG2" s="88"/>
-      <c r="BH2" s="91"/>
-      <c r="BI2" s="87" t="s">
+      <c r="BC2" s="101"/>
+      <c r="BD2" s="101"/>
+      <c r="BE2" s="101"/>
+      <c r="BF2" s="101"/>
+      <c r="BG2" s="101"/>
+      <c r="BH2" s="104"/>
+      <c r="BI2" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="BJ2" s="88"/>
-      <c r="BK2" s="88"/>
-      <c r="BL2" s="88"/>
-      <c r="BM2" s="88"/>
-      <c r="BN2" s="88"/>
-      <c r="BO2" s="87" t="s">
+      <c r="BJ2" s="101"/>
+      <c r="BK2" s="101"/>
+      <c r="BL2" s="101"/>
+      <c r="BM2" s="101"/>
+      <c r="BN2" s="101"/>
+      <c r="BO2" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="BP2" s="88"/>
-      <c r="BQ2" s="88"/>
-      <c r="BR2" s="88"/>
-      <c r="BS2" s="88"/>
-      <c r="BT2" s="88"/>
-      <c r="BU2" s="87" t="s">
+      <c r="BP2" s="101"/>
+      <c r="BQ2" s="101"/>
+      <c r="BR2" s="101"/>
+      <c r="BS2" s="101"/>
+      <c r="BT2" s="101"/>
+      <c r="BU2" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="BV2" s="88"/>
-      <c r="BW2" s="88"/>
-      <c r="BX2" s="88"/>
-      <c r="BY2" s="88"/>
-      <c r="BZ2" s="88"/>
-      <c r="CA2" s="87" t="s">
+      <c r="BV2" s="101"/>
+      <c r="BW2" s="101"/>
+      <c r="BX2" s="101"/>
+      <c r="BY2" s="101"/>
+      <c r="BZ2" s="101"/>
+      <c r="CA2" s="100" t="s">
         <v>756</v>
       </c>
-      <c r="CB2" s="88"/>
-      <c r="CC2" s="88"/>
-      <c r="CD2" s="88"/>
-      <c r="CE2" s="88"/>
-      <c r="CF2" s="88"/>
+      <c r="CB2" s="101"/>
+      <c r="CC2" s="101"/>
+      <c r="CD2" s="101"/>
+      <c r="CE2" s="101"/>
+      <c r="CF2" s="101"/>
       <c r="CG2" s="1"/>
       <c r="CH2" s="1"/>
       <c r="CI2" s="1"/>
@@ -20202,7 +20206,7 @@
       <c r="I3" s="24" t="s">
         <v>770</v>
       </c>
-      <c r="J3" s="90"/>
+      <c r="J3" s="103"/>
       <c r="K3" s="56" t="s">
         <v>772</v>
       </c>
@@ -20350,7 +20354,7 @@
       <c r="BG3" s="9" t="s">
         <v>755</v>
       </c>
-      <c r="BH3" s="92"/>
+      <c r="BH3" s="105"/>
       <c r="BI3" s="18" t="s">
         <v>752</v>
       </c>
@@ -20469,7 +20473,7 @@
       <c r="D4" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="118">
+      <c r="E4" s="91">
         <f>_xlfn.XLOOKUP(C4,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>0.8666666666666667</v>
       </c>
@@ -20560,7 +20564,7 @@
         <f>AVERAGE(BB4:BF4)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="BH4" s="93"/>
+      <c r="BH4" s="106"/>
       <c r="BI4" s="66"/>
       <c r="BJ4" s="61"/>
       <c r="BK4" s="61"/>
@@ -20643,14 +20647,14 @@
       <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="118">
+      <c r="E5" s="91">
         <f>_xlfn.XLOOKUP(C5,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F5" s="2">
         <v>1</v>
       </c>
-      <c r="G5" s="124">
+      <c r="G5" s="97">
         <f>H5+E5*10+F5*20</f>
         <v>100</v>
       </c>
@@ -20819,7 +20823,7 @@
         <f t="shared" ref="BG5:BG34" si="10">AVERAGE(BB5:BF5)</f>
         <v>0.45</v>
       </c>
-      <c r="BH5" s="94"/>
+      <c r="BH5" s="107"/>
       <c r="BI5" s="45"/>
       <c r="BJ5" s="7"/>
       <c r="BK5" s="7"/>
@@ -20902,14 +20906,14 @@
       <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="118">
+      <c r="E6" s="91">
         <f>_xlfn.XLOOKUP(C6,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
       </c>
-      <c r="G6" s="124">
+      <c r="G6" s="97">
         <f t="shared" ref="G6:G35" si="15">H6+E6*10+F6*20</f>
         <v>94.82</v>
       </c>
@@ -21078,7 +21082,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH6" s="94"/>
+      <c r="BH6" s="107"/>
       <c r="BI6" s="44"/>
       <c r="BJ6" s="5"/>
       <c r="BK6" s="5"/>
@@ -21161,14 +21165,14 @@
       <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="118">
+      <c r="E7" s="91">
         <f>_xlfn.XLOOKUP(C7,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F7" s="2">
         <v>1</v>
       </c>
-      <c r="G7" s="124">
+      <c r="G7" s="97">
         <f t="shared" si="15"/>
         <v>32.799999999999997</v>
       </c>
@@ -21337,7 +21341,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="BH7" s="94"/>
+      <c r="BH7" s="107"/>
       <c r="BI7" s="45"/>
       <c r="BJ7" s="7"/>
       <c r="BK7" s="7"/>
@@ -21420,14 +21424,14 @@
       <c r="D8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="118">
+      <c r="E8" s="91">
         <f>_xlfn.XLOOKUP(C8,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
       </c>
-      <c r="G8" s="124">
+      <c r="G8" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -21596,7 +21600,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH8" s="94"/>
+      <c r="BH8" s="107"/>
       <c r="BI8" s="44"/>
       <c r="BJ8" s="5"/>
       <c r="BK8" s="5"/>
@@ -21679,14 +21683,14 @@
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="118">
+      <c r="E9" s="91">
         <f>_xlfn.XLOOKUP(C9,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F9" s="2">
         <v>1</v>
       </c>
-      <c r="G9" s="124">
+      <c r="G9" s="97">
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
@@ -21855,7 +21859,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH9" s="94"/>
+      <c r="BH9" s="107"/>
       <c r="BI9" s="45"/>
       <c r="BJ9" s="7"/>
       <c r="BK9" s="7"/>
@@ -21938,14 +21942,14 @@
       <c r="D10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="118">
+      <c r="E10" s="91">
         <f>_xlfn.XLOOKUP(C10,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
       </c>
-      <c r="G10" s="124">
+      <c r="G10" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -22114,7 +22118,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH10" s="94"/>
+      <c r="BH10" s="107"/>
       <c r="BI10" s="44"/>
       <c r="BJ10" s="5"/>
       <c r="BK10" s="5"/>
@@ -22197,14 +22201,14 @@
       <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="118">
+      <c r="E11" s="91">
         <f>_xlfn.XLOOKUP(C11,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F11" s="2">
         <v>1</v>
       </c>
-      <c r="G11" s="124">
+      <c r="G11" s="97">
         <f t="shared" si="15"/>
         <v>53.099999999999994</v>
       </c>
@@ -22373,7 +22377,7 @@
         <f t="shared" si="10"/>
         <v>0.1</v>
       </c>
-      <c r="BH11" s="94"/>
+      <c r="BH11" s="107"/>
       <c r="BI11" s="45"/>
       <c r="BJ11" s="7"/>
       <c r="BK11" s="7"/>
@@ -22456,14 +22460,14 @@
       <c r="D12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="118">
+      <c r="E12" s="91">
         <f>_xlfn.XLOOKUP(C12,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
       </c>
-      <c r="G12" s="124">
+      <c r="G12" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -22632,7 +22636,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH12" s="94"/>
+      <c r="BH12" s="107"/>
       <c r="BI12" s="44"/>
       <c r="BJ12" s="5"/>
       <c r="BK12" s="5"/>
@@ -22715,14 +22719,14 @@
       <c r="D13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E13" s="118">
+      <c r="E13" s="91">
         <f>_xlfn.XLOOKUP(C13,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>0.8</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="124">
+      <c r="G13" s="97">
         <f t="shared" si="15"/>
         <v>28</v>
       </c>
@@ -22891,7 +22895,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH13" s="94"/>
+      <c r="BH13" s="107"/>
       <c r="BI13" s="45"/>
       <c r="BJ13" s="7"/>
       <c r="BK13" s="7"/>
@@ -22974,14 +22978,14 @@
       <c r="D14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="118">
+      <c r="E14" s="91">
         <f>_xlfn.XLOOKUP(C14,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
       </c>
-      <c r="G14" s="124">
+      <c r="G14" s="97">
         <f t="shared" si="15"/>
         <v>79</v>
       </c>
@@ -23150,7 +23154,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH14" s="94"/>
+      <c r="BH14" s="107"/>
       <c r="BI14" s="44"/>
       <c r="BJ14" s="5"/>
       <c r="BK14" s="5"/>
@@ -23233,14 +23237,14 @@
       <c r="D15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="118">
+      <c r="E15" s="91">
         <f>_xlfn.XLOOKUP(C15,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>0.93333333333333335</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
-      <c r="G15" s="124">
+      <c r="G15" s="97">
         <f t="shared" si="15"/>
         <v>77.633333333333326</v>
       </c>
@@ -23409,7 +23413,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH15" s="94"/>
+      <c r="BH15" s="107"/>
       <c r="BI15" s="45"/>
       <c r="BJ15" s="7"/>
       <c r="BK15" s="7"/>
@@ -23492,14 +23496,14 @@
       <c r="D16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="118">
+      <c r="E16" s="91">
         <f>_xlfn.XLOOKUP(C16,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
-      <c r="G16" s="124">
+      <c r="G16" s="97">
         <f t="shared" si="15"/>
         <v>63.04</v>
       </c>
@@ -23668,7 +23672,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH16" s="94"/>
+      <c r="BH16" s="107"/>
       <c r="BI16" s="44"/>
       <c r="BJ16" s="5"/>
       <c r="BK16" s="5"/>
@@ -23751,14 +23755,14 @@
       <c r="D17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="118">
+      <c r="E17" s="91">
         <f>_xlfn.XLOOKUP(C17,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
       </c>
-      <c r="G17" s="124">
+      <c r="G17" s="97">
         <f t="shared" si="15"/>
         <v>60.974999999999994</v>
       </c>
@@ -23927,7 +23931,7 @@
         <f t="shared" si="10"/>
         <v>0.2</v>
       </c>
-      <c r="BH17" s="94"/>
+      <c r="BH17" s="107"/>
       <c r="BI17" s="45"/>
       <c r="BJ17" s="7"/>
       <c r="BK17" s="7"/>
@@ -24010,14 +24014,14 @@
       <c r="D18" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E18" s="118">
+      <c r="E18" s="91">
         <f>_xlfn.XLOOKUP(C18,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
       </c>
-      <c r="G18" s="124">
+      <c r="G18" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -24186,7 +24190,7 @@
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="BH18" s="94"/>
+      <c r="BH18" s="107"/>
       <c r="BI18" s="44"/>
       <c r="BJ18" s="5"/>
       <c r="BK18" s="5"/>
@@ -24271,9 +24275,9 @@
       </c>
       <c r="E19" s="83"/>
       <c r="F19" s="83"/>
-      <c r="G19" s="125"/>
+      <c r="G19" s="98"/>
       <c r="H19" s="63" t="e">
-        <f t="shared" ref="G5:H34" si="17">J19*0.7</f>
+        <f t="shared" ref="H19:H28" si="17">J19*0.7</f>
         <v>#DIV/0!</v>
       </c>
       <c r="I19" s="64" t="e">
@@ -24357,7 +24361,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BH19" s="94"/>
+      <c r="BH19" s="107"/>
       <c r="BI19" s="66"/>
       <c r="BJ19" s="61"/>
       <c r="BK19" s="61"/>
@@ -24440,14 +24444,14 @@
       <c r="D20" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E20" s="118">
+      <c r="E20" s="91">
         <f>_xlfn.XLOOKUP(C20,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
       </c>
-      <c r="G20" s="124">
+      <c r="G20" s="97">
         <f t="shared" si="15"/>
         <v>75.22</v>
       </c>
@@ -24616,7 +24620,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH20" s="94"/>
+      <c r="BH20" s="107"/>
       <c r="BI20" s="44"/>
       <c r="BJ20" s="5"/>
       <c r="BK20" s="5"/>
@@ -24699,14 +24703,14 @@
       <c r="D21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E21" s="118">
+      <c r="E21" s="91">
         <f>_xlfn.XLOOKUP(C21,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F21" s="2">
         <v>1</v>
       </c>
-      <c r="G21" s="124">
+      <c r="G21" s="97">
         <f t="shared" si="15"/>
         <v>94.75</v>
       </c>
@@ -24875,7 +24879,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH21" s="94"/>
+      <c r="BH21" s="107"/>
       <c r="BI21" s="45"/>
       <c r="BJ21" s="7"/>
       <c r="BK21" s="7"/>
@@ -24958,14 +24962,14 @@
       <c r="D22" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="118">
+      <c r="E22" s="91">
         <f>_xlfn.XLOOKUP(C22,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
       </c>
-      <c r="G22" s="124">
+      <c r="G22" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -25134,7 +25138,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH22" s="94"/>
+      <c r="BH22" s="107"/>
       <c r="BI22" s="44"/>
       <c r="BJ22" s="5"/>
       <c r="BK22" s="5"/>
@@ -25217,14 +25221,14 @@
       <c r="D23" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="118">
+      <c r="E23" s="91">
         <f>_xlfn.XLOOKUP(C23,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F23" s="2">
         <v>1</v>
       </c>
-      <c r="G23" s="124">
+      <c r="G23" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -25393,7 +25397,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH23" s="94"/>
+      <c r="BH23" s="107"/>
       <c r="BI23" s="45"/>
       <c r="BJ23" s="7"/>
       <c r="BK23" s="7"/>
@@ -25476,14 +25480,14 @@
       <c r="D24" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E24" s="118">
+      <c r="E24" s="91">
         <f>_xlfn.XLOOKUP(C24,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
       </c>
-      <c r="G24" s="124">
+      <c r="G24" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -25654,7 +25658,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH24" s="94"/>
+      <c r="BH24" s="107"/>
       <c r="BI24" s="44"/>
       <c r="BJ24" s="5"/>
       <c r="BK24" s="5"/>
@@ -25737,14 +25741,14 @@
       <c r="D25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E25" s="118">
+      <c r="E25" s="91">
         <f>_xlfn.XLOOKUP(C25,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F25" s="2">
         <v>1</v>
       </c>
-      <c r="G25" s="124">
+      <c r="G25" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -25913,7 +25917,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH25" s="94"/>
+      <c r="BH25" s="107"/>
       <c r="BI25" s="45"/>
       <c r="BJ25" s="7"/>
       <c r="BK25" s="7"/>
@@ -25996,14 +26000,14 @@
       <c r="D26" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E26" s="118">
+      <c r="E26" s="91">
         <f>_xlfn.XLOOKUP(C26,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
       </c>
-      <c r="G26" s="124">
+      <c r="G26" s="97">
         <f t="shared" si="15"/>
         <v>90.199999999999989</v>
       </c>
@@ -26174,7 +26178,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH26" s="94"/>
+      <c r="BH26" s="107"/>
       <c r="BI26" s="44"/>
       <c r="BJ26" s="5"/>
       <c r="BK26" s="5"/>
@@ -26257,14 +26261,14 @@
       <c r="D27" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="118">
+      <c r="E27" s="91">
         <f>_xlfn.XLOOKUP(C27,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F27" s="2">
         <v>1</v>
       </c>
-      <c r="G27" s="124">
+      <c r="G27" s="97">
         <f t="shared" si="15"/>
         <v>96.5</v>
       </c>
@@ -26433,7 +26437,7 @@
         <f t="shared" si="10"/>
         <v>0.8</v>
       </c>
-      <c r="BH27" s="94"/>
+      <c r="BH27" s="107"/>
       <c r="BI27" s="45"/>
       <c r="BJ27" s="7"/>
       <c r="BK27" s="7"/>
@@ -26523,7 +26527,7 @@
       <c r="F28" s="83">
         <v>1</v>
       </c>
-      <c r="G28" s="126" t="e">
+      <c r="G28" s="99" t="e">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
@@ -26612,7 +26616,7 @@
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="BH28" s="94"/>
+      <c r="BH28" s="107"/>
       <c r="BI28" s="66"/>
       <c r="BJ28" s="61"/>
       <c r="BK28" s="61"/>
@@ -26695,14 +26699,14 @@
       <c r="D29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="118">
+      <c r="E29" s="91">
         <f>_xlfn.XLOOKUP(C29,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F29" s="2">
         <v>1</v>
       </c>
-      <c r="G29" s="124">
+      <c r="G29" s="97">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -26871,7 +26875,7 @@
         <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="BH29" s="94"/>
+      <c r="BH29" s="107"/>
       <c r="BI29" s="45"/>
       <c r="BJ29" s="7"/>
       <c r="BK29" s="7"/>
@@ -26954,14 +26958,14 @@
       <c r="D30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E30" s="118">
+      <c r="E30" s="91">
         <f>_xlfn.XLOOKUP(C30,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F30" s="3">
         <v>1</v>
       </c>
-      <c r="G30" s="124">
+      <c r="G30" s="97">
         <f t="shared" si="15"/>
         <v>56.879999999999995</v>
       </c>
@@ -27130,7 +27134,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH30" s="94"/>
+      <c r="BH30" s="107"/>
       <c r="BI30" s="44"/>
       <c r="BJ30" s="5"/>
       <c r="BK30" s="5"/>
@@ -27213,14 +27217,14 @@
       <c r="D31" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="118">
+      <c r="E31" s="91">
         <f>_xlfn.XLOOKUP(C31,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F31" s="2">
         <v>1</v>
       </c>
-      <c r="G31" s="124">
+      <c r="G31" s="97">
         <f t="shared" si="15"/>
         <v>41.9</v>
       </c>
@@ -27389,7 +27393,7 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="BH31" s="94"/>
+      <c r="BH31" s="107"/>
       <c r="BI31" s="45"/>
       <c r="BJ31" s="7"/>
       <c r="BK31" s="7"/>
@@ -27476,14 +27480,14 @@
       <c r="D32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E32" s="118">
+      <c r="E32" s="91">
         <f>_xlfn.XLOOKUP(C32,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F32" s="3">
         <v>1</v>
       </c>
-      <c r="G32" s="124">
+      <c r="G32" s="97">
         <f t="shared" si="15"/>
         <v>54.36</v>
       </c>
@@ -27652,7 +27656,7 @@
         <f t="shared" si="10"/>
         <v>0.74</v>
       </c>
-      <c r="BH32" s="94"/>
+      <c r="BH32" s="107"/>
       <c r="BI32" s="44"/>
       <c r="BJ32" s="5"/>
       <c r="BK32" s="5"/>
@@ -27735,14 +27739,14 @@
       <c r="D33" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E33" s="118">
+      <c r="E33" s="91">
         <f>_xlfn.XLOOKUP(C33,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F33" s="2">
         <v>1</v>
       </c>
-      <c r="G33" s="124">
+      <c r="G33" s="97">
         <f t="shared" si="15"/>
         <v>47.849999999999994</v>
       </c>
@@ -27911,7 +27915,7 @@
         <f t="shared" si="10"/>
         <v>0.1</v>
       </c>
-      <c r="BH33" s="94"/>
+      <c r="BH33" s="107"/>
       <c r="BI33" s="45"/>
       <c r="BJ33" s="7"/>
       <c r="BK33" s="7"/>
@@ -27994,14 +27998,14 @@
       <c r="D34" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E34" s="118">
+      <c r="E34" s="91">
         <f>_xlfn.XLOOKUP(C34,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
       </c>
-      <c r="G34" s="124">
+      <c r="G34" s="97">
         <f t="shared" si="15"/>
         <v>47.5</v>
       </c>
@@ -28170,7 +28174,7 @@
         <f t="shared" si="10"/>
         <v>0.1</v>
       </c>
-      <c r="BH34" s="94"/>
+      <c r="BH34" s="107"/>
       <c r="BI34" s="44"/>
       <c r="BJ34" s="5"/>
       <c r="BK34" s="5"/>
@@ -28244,14 +28248,14 @@
       <c r="C35" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="E35" s="118">
+      <c r="E35" s="91">
         <f>_xlfn.XLOOKUP(C35,'[1]9M_CD'!$C:$C,'[1]9M_CD'!$I:$I,"")</f>
         <v>1</v>
       </c>
-      <c r="F35" s="121">
-        <v>1</v>
-      </c>
-      <c r="G35" s="124">
+      <c r="F35" s="94">
+        <v>1</v>
+      </c>
+      <c r="G35" s="97">
         <f t="shared" si="15"/>
         <v>76.13</v>
       </c>
@@ -28428,11 +28432,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="BI2:BN2"/>
-    <mergeCell ref="BO2:BT2"/>
-    <mergeCell ref="BU2:BZ2"/>
-    <mergeCell ref="CA2:CF2"/>
-    <mergeCell ref="BH4:BH34"/>
     <mergeCell ref="L1:N1"/>
     <mergeCell ref="BH1:BH3"/>
     <mergeCell ref="J2:J3"/>
@@ -28444,6 +28443,11 @@
     <mergeCell ref="AP2:AU2"/>
     <mergeCell ref="AV2:BA2"/>
     <mergeCell ref="BB2:BG2"/>
+    <mergeCell ref="BI2:BN2"/>
+    <mergeCell ref="BO2:BT2"/>
+    <mergeCell ref="BU2:BZ2"/>
+    <mergeCell ref="CA2:CF2"/>
+    <mergeCell ref="BH4:BH34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -28929,7 +28933,7 @@
         <f>_xlfn.XLOOKUP(C4,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L4" s="122">
+      <c r="L4" s="95">
         <f>M4+J4*20+K4*10</f>
         <v>83.55</v>
       </c>
@@ -29203,7 +29207,7 @@
         <f>_xlfn.XLOOKUP(C5,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L5" s="122">
+      <c r="L5" s="95">
         <f t="shared" ref="L5:L41" si="0">M5+J5*20+K5*10</f>
         <v>94.96</v>
       </c>
@@ -29472,7 +29476,7 @@
         <f>_xlfn.XLOOKUP(C6,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.9285714285714286</v>
       </c>
-      <c r="L6" s="122">
+      <c r="L6" s="95">
         <f t="shared" si="0"/>
         <v>99.285714285714292</v>
       </c>
@@ -29739,7 +29743,7 @@
         <f>_xlfn.XLOOKUP(C7,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L7" s="122">
+      <c r="L7" s="95">
         <f t="shared" si="0"/>
         <v>42.879999999999995</v>
       </c>
@@ -30008,7 +30012,7 @@
         <f>_xlfn.XLOOKUP(C8,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L8" s="122">
+      <c r="L8" s="95">
         <f t="shared" si="0"/>
         <v>66.574999999999989</v>
       </c>
@@ -30277,7 +30281,7 @@
         <f>_xlfn.XLOOKUP(C9,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L9" s="122">
+      <c r="L9" s="95">
         <f t="shared" si="0"/>
         <v>47.325000000000003</v>
       </c>
@@ -30547,7 +30551,7 @@
         <f>_xlfn.XLOOKUP(C10,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L10" s="122">
+      <c r="L10" s="95">
         <f t="shared" si="0"/>
         <v>59.224999999999994</v>
       </c>
@@ -30816,7 +30820,7 @@
         <f>_xlfn.XLOOKUP(C11,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="95">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -31079,7 +31083,7 @@
         <f>_xlfn.XLOOKUP(C12,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L12" s="122">
+      <c r="L12" s="95">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -31346,7 +31350,7 @@
         <f>_xlfn.XLOOKUP(C13,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.9285714285714286</v>
       </c>
-      <c r="L13" s="122">
+      <c r="L13" s="95">
         <f t="shared" si="0"/>
         <v>29.985714285714288</v>
       </c>
@@ -31613,7 +31617,7 @@
         <f>_xlfn.XLOOKUP(C14,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L14" s="122">
+      <c r="L14" s="95">
         <f t="shared" si="0"/>
         <v>98.424999999999997</v>
       </c>
@@ -31905,7 +31909,7 @@
         <f>_xlfn.XLOOKUP(C15,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L15" s="122">
+      <c r="L15" s="95">
         <f t="shared" si="0"/>
         <v>38.4</v>
       </c>
@@ -32174,7 +32178,7 @@
         <f>_xlfn.XLOOKUP(C16,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L16" s="122">
+      <c r="L16" s="95">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
@@ -32443,7 +32447,7 @@
         <f>_xlfn.XLOOKUP(C17,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L17" s="122">
+      <c r="L17" s="95">
         <f t="shared" si="0"/>
         <v>98.424999999999997</v>
       </c>
@@ -32710,7 +32714,7 @@
         <f>_xlfn.XLOOKUP(C18,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L18" s="122">
+      <c r="L18" s="95">
         <f t="shared" si="0"/>
         <v>61.849999999999994</v>
       </c>
@@ -32966,7 +32970,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="59"/>
-      <c r="L19" s="122"/>
+      <c r="L19" s="95"/>
       <c r="M19" s="30"/>
       <c r="N19" s="64" t="e">
         <f t="shared" si="2"/>
@@ -33144,7 +33148,7 @@
         <v>1</v>
       </c>
       <c r="K20" s="59"/>
-      <c r="L20" s="122"/>
+      <c r="L20" s="95"/>
       <c r="M20" s="30"/>
       <c r="N20" s="64" t="e">
         <f t="shared" si="2"/>
@@ -33327,7 +33331,7 @@
         <f>_xlfn.XLOOKUP(C21,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L21" s="122">
+      <c r="L21" s="95">
         <f t="shared" si="0"/>
         <v>44.7</v>
       </c>
@@ -33594,7 +33598,7 @@
         <f>_xlfn.XLOOKUP(C22,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L22" s="122">
+      <c r="L22" s="95">
         <f t="shared" si="0"/>
         <v>87.4</v>
       </c>
@@ -33863,7 +33867,7 @@
         <f>_xlfn.XLOOKUP(C23,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L23" s="122">
+      <c r="L23" s="95">
         <f t="shared" si="0"/>
         <v>63.704999999999998</v>
       </c>
@@ -34132,7 +34136,7 @@
         <f>_xlfn.XLOOKUP(C24,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L24" s="122">
+      <c r="L24" s="95">
         <f t="shared" si="0"/>
         <v>71.474999999999994</v>
       </c>
@@ -34414,7 +34418,7 @@
         <f>_xlfn.XLOOKUP(C25,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L25" s="122">
+      <c r="L25" s="95">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -34683,7 +34687,7 @@
         <f>_xlfn.XLOOKUP(C26,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L26" s="122">
+      <c r="L26" s="95">
         <f t="shared" si="0"/>
         <v>78.474999999999994</v>
       </c>
@@ -34950,7 +34954,7 @@
         <f>_xlfn.XLOOKUP(C27,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L27" s="122">
+      <c r="L27" s="95">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
@@ -35215,7 +35219,7 @@
         <f>_xlfn.XLOOKUP(C28,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.9285714285714286</v>
       </c>
-      <c r="L28" s="122">
+      <c r="L28" s="95">
         <f t="shared" si="0"/>
         <v>82.625714285714295</v>
       </c>
@@ -35484,7 +35488,7 @@
         <f>_xlfn.XLOOKUP(C29,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.5</v>
       </c>
-      <c r="L29" s="122">
+      <c r="L29" s="95">
         <f t="shared" si="0"/>
         <v>70.5</v>
       </c>
@@ -35753,7 +35757,7 @@
         <f>_xlfn.XLOOKUP(C30,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.92307692307692313</v>
       </c>
-      <c r="L30" s="122">
+      <c r="L30" s="95">
         <f t="shared" si="0"/>
         <v>68.500769230769222</v>
       </c>
@@ -36020,7 +36024,7 @@
         <f>_xlfn.XLOOKUP(C31,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L31" s="122">
+      <c r="L31" s="95">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -36289,7 +36293,7 @@
         <f>_xlfn.XLOOKUP(C32,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L32" s="122">
+      <c r="L32" s="95">
         <f t="shared" si="0"/>
         <v>51.56</v>
       </c>
@@ -36558,7 +36562,7 @@
         <f>_xlfn.XLOOKUP(C33,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L33" s="122">
+      <c r="L33" s="95">
         <f t="shared" si="0"/>
         <v>99.3</v>
       </c>
@@ -36821,7 +36825,7 @@
         <f>_xlfn.XLOOKUP(C34,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.9285714285714286</v>
       </c>
-      <c r="L34" s="122">
+      <c r="L34" s="95">
         <f t="shared" si="0"/>
         <v>45.735714285714288</v>
       </c>
@@ -37083,7 +37087,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="59"/>
-      <c r="L35" s="122"/>
+      <c r="L35" s="95"/>
       <c r="M35" s="30"/>
       <c r="N35" s="64" t="e">
         <f t="shared" si="2"/>
@@ -37264,7 +37268,7 @@
         <f>_xlfn.XLOOKUP(C36,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L36" s="122">
+      <c r="L36" s="95">
         <f t="shared" si="0"/>
         <v>74.8</v>
       </c>
@@ -37533,7 +37537,7 @@
         <f>_xlfn.XLOOKUP(C37,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L37" s="122">
+      <c r="L37" s="95">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -37822,7 +37826,7 @@
         <f>_xlfn.XLOOKUP(C38,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L38" s="122">
+      <c r="L38" s="95">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
@@ -38089,7 +38093,7 @@
         <f>_xlfn.XLOOKUP(C39,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>1</v>
       </c>
-      <c r="L39" s="122">
+      <c r="L39" s="95">
         <f t="shared" si="0"/>
         <v>59.4</v>
       </c>
@@ -38349,7 +38353,7 @@
         <v>1</v>
       </c>
       <c r="K40" s="59"/>
-      <c r="L40" s="122"/>
+      <c r="L40" s="95"/>
       <c r="M40" s="30"/>
       <c r="N40" s="64" t="e">
         <f t="shared" si="2"/>
@@ -38506,11 +38510,11 @@
       <c r="J41" s="4">
         <v>1</v>
       </c>
-      <c r="K41" s="119">
+      <c r="K41" s="92">
         <f>_xlfn.XLOOKUP(C41,'[1]4B_CD'!$C:$C,'[1]4B_CD'!$J:$J,"")</f>
         <v>0.5</v>
       </c>
-      <c r="L41" s="122">
+      <c r="L41" s="95">
         <f t="shared" si="0"/>
         <v>73.02</v>
       </c>
@@ -38836,53 +38840,53 @@
       <c r="P1" s="60" t="s">
         <v>751</v>
       </c>
-      <c r="Q1" s="112"/>
-      <c r="R1" s="112"/>
-      <c r="S1" s="112"/>
-      <c r="T1" s="112"/>
-      <c r="U1" s="113"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="110"/>
-      <c r="X1" s="110"/>
-      <c r="Y1" s="110"/>
-      <c r="Z1" s="110"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="110"/>
-      <c r="AD1" s="110"/>
-      <c r="AE1" s="110"/>
-      <c r="AF1" s="110"/>
-      <c r="AG1" s="111"/>
-      <c r="AH1" s="109"/>
-      <c r="AI1" s="110"/>
-      <c r="AJ1" s="110"/>
-      <c r="AK1" s="110"/>
-      <c r="AL1" s="110"/>
-      <c r="AM1" s="111"/>
-      <c r="AN1" s="109"/>
-      <c r="AO1" s="110"/>
-      <c r="AP1" s="110"/>
-      <c r="AQ1" s="110"/>
-      <c r="AR1" s="110"/>
-      <c r="AS1" s="111"/>
-      <c r="AT1" s="109"/>
-      <c r="AU1" s="110"/>
-      <c r="AV1" s="110"/>
-      <c r="AW1" s="110"/>
-      <c r="AX1" s="110"/>
-      <c r="AY1" s="111"/>
-      <c r="AZ1" s="109"/>
-      <c r="BA1" s="110"/>
-      <c r="BB1" s="110"/>
-      <c r="BC1" s="110"/>
-      <c r="BD1" s="110"/>
-      <c r="BE1" s="111"/>
-      <c r="BF1" s="109"/>
-      <c r="BG1" s="110"/>
-      <c r="BH1" s="110"/>
-      <c r="BI1" s="110"/>
-      <c r="BJ1" s="110"/>
-      <c r="BK1" s="111"/>
+      <c r="Q1" s="122"/>
+      <c r="R1" s="122"/>
+      <c r="S1" s="122"/>
+      <c r="T1" s="122"/>
+      <c r="U1" s="123"/>
+      <c r="V1" s="124"/>
+      <c r="W1" s="125"/>
+      <c r="X1" s="125"/>
+      <c r="Y1" s="125"/>
+      <c r="Z1" s="125"/>
+      <c r="AA1" s="126"/>
+      <c r="AB1" s="124"/>
+      <c r="AC1" s="125"/>
+      <c r="AD1" s="125"/>
+      <c r="AE1" s="125"/>
+      <c r="AF1" s="125"/>
+      <c r="AG1" s="126"/>
+      <c r="AH1" s="124"/>
+      <c r="AI1" s="125"/>
+      <c r="AJ1" s="125"/>
+      <c r="AK1" s="125"/>
+      <c r="AL1" s="125"/>
+      <c r="AM1" s="126"/>
+      <c r="AN1" s="124"/>
+      <c r="AO1" s="125"/>
+      <c r="AP1" s="125"/>
+      <c r="AQ1" s="125"/>
+      <c r="AR1" s="125"/>
+      <c r="AS1" s="126"/>
+      <c r="AT1" s="124"/>
+      <c r="AU1" s="125"/>
+      <c r="AV1" s="125"/>
+      <c r="AW1" s="125"/>
+      <c r="AX1" s="125"/>
+      <c r="AY1" s="126"/>
+      <c r="AZ1" s="124"/>
+      <c r="BA1" s="125"/>
+      <c r="BB1" s="125"/>
+      <c r="BC1" s="125"/>
+      <c r="BD1" s="125"/>
+      <c r="BE1" s="126"/>
+      <c r="BF1" s="124"/>
+      <c r="BG1" s="125"/>
+      <c r="BH1" s="125"/>
+      <c r="BI1" s="125"/>
+      <c r="BJ1" s="125"/>
+      <c r="BK1" s="126"/>
       <c r="BL1" s="49" t="s">
         <v>769</v>
       </c>
@@ -38912,70 +38916,70 @@
         <v>758</v>
       </c>
       <c r="O2" s="36"/>
-      <c r="P2" s="98" t="s">
+      <c r="P2" s="109" t="s">
         <v>759</v>
       </c>
-      <c r="Q2" s="99"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="99"/>
-      <c r="T2" s="99"/>
-      <c r="U2" s="100"/>
-      <c r="V2" s="101" t="s">
+      <c r="Q2" s="110"/>
+      <c r="R2" s="110"/>
+      <c r="S2" s="110"/>
+      <c r="T2" s="110"/>
+      <c r="U2" s="111"/>
+      <c r="V2" s="112" t="s">
         <v>760</v>
       </c>
-      <c r="W2" s="99"/>
-      <c r="X2" s="99"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="99"/>
-      <c r="AA2" s="102"/>
-      <c r="AB2" s="98" t="s">
+      <c r="W2" s="110"/>
+      <c r="X2" s="110"/>
+      <c r="Y2" s="110"/>
+      <c r="Z2" s="110"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="109" t="s">
         <v>761</v>
       </c>
-      <c r="AC2" s="99"/>
-      <c r="AD2" s="99"/>
-      <c r="AE2" s="99"/>
-      <c r="AF2" s="99"/>
-      <c r="AG2" s="100"/>
-      <c r="AH2" s="101" t="s">
+      <c r="AC2" s="110"/>
+      <c r="AD2" s="110"/>
+      <c r="AE2" s="110"/>
+      <c r="AF2" s="110"/>
+      <c r="AG2" s="111"/>
+      <c r="AH2" s="112" t="s">
         <v>762</v>
       </c>
-      <c r="AI2" s="99"/>
-      <c r="AJ2" s="99"/>
-      <c r="AK2" s="99"/>
-      <c r="AL2" s="99"/>
-      <c r="AM2" s="102"/>
-      <c r="AN2" s="98" t="s">
+      <c r="AI2" s="110"/>
+      <c r="AJ2" s="110"/>
+      <c r="AK2" s="110"/>
+      <c r="AL2" s="110"/>
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="109" t="s">
         <v>765</v>
       </c>
-      <c r="AO2" s="99"/>
-      <c r="AP2" s="99"/>
-      <c r="AQ2" s="99"/>
-      <c r="AR2" s="99"/>
-      <c r="AS2" s="100"/>
-      <c r="AT2" s="101" t="s">
+      <c r="AO2" s="110"/>
+      <c r="AP2" s="110"/>
+      <c r="AQ2" s="110"/>
+      <c r="AR2" s="110"/>
+      <c r="AS2" s="111"/>
+      <c r="AT2" s="112" t="s">
         <v>766</v>
       </c>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="99"/>
-      <c r="AW2" s="99"/>
-      <c r="AX2" s="99"/>
-      <c r="AY2" s="100"/>
-      <c r="AZ2" s="101" t="s">
+      <c r="AU2" s="110"/>
+      <c r="AV2" s="110"/>
+      <c r="AW2" s="110"/>
+      <c r="AX2" s="110"/>
+      <c r="AY2" s="111"/>
+      <c r="AZ2" s="112" t="s">
         <v>767</v>
       </c>
-      <c r="BA2" s="99"/>
-      <c r="BB2" s="99"/>
-      <c r="BC2" s="99"/>
-      <c r="BD2" s="99"/>
-      <c r="BE2" s="100"/>
-      <c r="BF2" s="101" t="s">
+      <c r="BA2" s="110"/>
+      <c r="BB2" s="110"/>
+      <c r="BC2" s="110"/>
+      <c r="BD2" s="110"/>
+      <c r="BE2" s="111"/>
+      <c r="BF2" s="112" t="s">
         <v>768</v>
       </c>
-      <c r="BG2" s="99"/>
-      <c r="BH2" s="99"/>
-      <c r="BI2" s="99"/>
-      <c r="BJ2" s="99"/>
-      <c r="BK2" s="99"/>
+      <c r="BG2" s="110"/>
+      <c r="BH2" s="110"/>
+      <c r="BI2" s="110"/>
+      <c r="BJ2" s="110"/>
+      <c r="BK2" s="110"/>
       <c r="BL2" s="49"/>
       <c r="BM2" s="26" t="s">
         <v>756</v>
@@ -39351,8 +39355,8 @@
       <c r="D4" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E4" s="103"/>
-      <c r="F4" s="104"/>
+      <c r="E4" s="116"/>
+      <c r="F4" s="117"/>
       <c r="G4" s="61"/>
       <c r="H4" s="61"/>
       <c r="I4" s="61"/>
@@ -39524,8 +39528,8 @@
       <c r="D5" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E5" s="105"/>
-      <c r="F5" s="106"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="119"/>
       <c r="G5" s="7">
         <v>1</v>
       </c>
@@ -39539,7 +39543,7 @@
       <c r="J5" s="7">
         <v>1</v>
       </c>
-      <c r="K5" s="123">
+      <c r="K5" s="96">
         <f>L5+I5*10+J5*20</f>
         <v>92.3</v>
       </c>
@@ -39802,8 +39806,8 @@
       <c r="D6" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E6" s="105"/>
-      <c r="F6" s="106"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="119"/>
       <c r="G6" s="5">
         <v>1</v>
       </c>
@@ -39817,7 +39821,7 @@
       <c r="J6" s="5">
         <v>1</v>
       </c>
-      <c r="K6" s="123">
+      <c r="K6" s="96">
         <f t="shared" ref="K6:K26" si="15">L6+I6*10+J6*20</f>
         <v>100</v>
       </c>
@@ -40067,8 +40071,8 @@
       <c r="D7" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="105"/>
-      <c r="F7" s="106"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="119"/>
       <c r="G7" s="7">
         <v>1</v>
       </c>
@@ -40082,7 +40086,7 @@
       <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="K7" s="123">
+      <c r="K7" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -40332,8 +40336,8 @@
       <c r="D8" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E8" s="105"/>
-      <c r="F8" s="106"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="119"/>
       <c r="G8" s="5">
         <v>1</v>
       </c>
@@ -40347,7 +40351,7 @@
       <c r="J8" s="5">
         <v>1</v>
       </c>
-      <c r="K8" s="123">
+      <c r="K8" s="96">
         <f t="shared" si="15"/>
         <v>97.899999999999991</v>
       </c>
@@ -40598,8 +40602,8 @@
       <c r="D9" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="105"/>
-      <c r="F9" s="106"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="119"/>
       <c r="G9" s="73">
         <v>1</v>
       </c>
@@ -40613,7 +40617,7 @@
       <c r="J9" s="73">
         <v>1</v>
       </c>
-      <c r="K9" s="123">
+      <c r="K9" s="96">
         <f t="shared" si="15"/>
         <v>84.6</v>
       </c>
@@ -40863,8 +40867,8 @@
       <c r="D10" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E10" s="105"/>
-      <c r="F10" s="106"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="119"/>
       <c r="G10" s="5">
         <v>1</v>
       </c>
@@ -40878,7 +40882,7 @@
       <c r="J10" s="5">
         <v>1</v>
       </c>
-      <c r="K10" s="123">
+      <c r="K10" s="96">
         <f t="shared" si="15"/>
         <v>86</v>
       </c>
@@ -41128,13 +41132,13 @@
       <c r="D11" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E11" s="105"/>
-      <c r="F11" s="106"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="119"/>
       <c r="G11" s="61"/>
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
       <c r="J11" s="61"/>
-      <c r="K11" s="123"/>
+      <c r="K11" s="96"/>
       <c r="L11" s="63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -41301,8 +41305,8 @@
       <c r="D12" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E12" s="105"/>
-      <c r="F12" s="106"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="119"/>
       <c r="G12" s="5">
         <v>1</v>
       </c>
@@ -41316,7 +41320,7 @@
       <c r="J12" s="5">
         <v>1</v>
       </c>
-      <c r="K12" s="123">
+      <c r="K12" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -41568,8 +41572,8 @@
       <c r="D13" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E13" s="105"/>
-      <c r="F13" s="106"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="119"/>
       <c r="G13" s="7">
         <v>1</v>
       </c>
@@ -41583,7 +41587,7 @@
       <c r="J13" s="7">
         <v>1</v>
       </c>
-      <c r="K13" s="123">
+      <c r="K13" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -41835,8 +41839,8 @@
       <c r="D14" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="105"/>
-      <c r="F14" s="106"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="119"/>
       <c r="G14" s="73">
         <v>1</v>
       </c>
@@ -41850,7 +41854,7 @@
       <c r="J14" s="73">
         <v>1</v>
       </c>
-      <c r="K14" s="123">
+      <c r="K14" s="96">
         <f t="shared" si="15"/>
         <v>49.599999999999994</v>
       </c>
@@ -42100,8 +42104,8 @@
       <c r="D15" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E15" s="105"/>
-      <c r="F15" s="106"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="119"/>
       <c r="G15" s="7">
         <v>1</v>
       </c>
@@ -42115,7 +42119,7 @@
       <c r="J15" s="7">
         <v>1</v>
       </c>
-      <c r="K15" s="123">
+      <c r="K15" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -42365,13 +42369,13 @@
       <c r="D16" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E16" s="105"/>
-      <c r="F16" s="106"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="119"/>
       <c r="G16" s="61"/>
       <c r="H16" s="61"/>
       <c r="I16" s="61"/>
       <c r="J16" s="61"/>
-      <c r="K16" s="123"/>
+      <c r="K16" s="96"/>
       <c r="L16" s="63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -42538,8 +42542,8 @@
       <c r="D17" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E17" s="105"/>
-      <c r="F17" s="106"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="119"/>
       <c r="G17" s="7">
         <v>1</v>
       </c>
@@ -42553,7 +42557,7 @@
       <c r="J17" s="7">
         <v>1</v>
       </c>
-      <c r="K17" s="123">
+      <c r="K17" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -42805,13 +42809,13 @@
       <c r="D18" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E18" s="105"/>
-      <c r="F18" s="106"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="119"/>
       <c r="G18" s="61"/>
       <c r="H18" s="61"/>
       <c r="I18" s="61"/>
       <c r="J18" s="61"/>
-      <c r="K18" s="123"/>
+      <c r="K18" s="96"/>
       <c r="L18" s="63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -42978,8 +42982,8 @@
       <c r="D19" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E19" s="105"/>
-      <c r="F19" s="106"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="119"/>
       <c r="G19" s="7">
         <v>1</v>
       </c>
@@ -42993,7 +42997,7 @@
       <c r="J19" s="7">
         <v>1</v>
       </c>
-      <c r="K19" s="123">
+      <c r="K19" s="96">
         <f t="shared" si="15"/>
         <v>47.849999999999994</v>
       </c>
@@ -43245,8 +43249,8 @@
       <c r="D20" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E20" s="105"/>
-      <c r="F20" s="106"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="119"/>
       <c r="G20" s="5">
         <v>1</v>
       </c>
@@ -43260,7 +43264,7 @@
       <c r="J20" s="5">
         <v>1</v>
       </c>
-      <c r="K20" s="123">
+      <c r="K20" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -43510,8 +43514,8 @@
       <c r="D21" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E21" s="105"/>
-      <c r="F21" s="106"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="119"/>
       <c r="G21" s="7">
         <v>1</v>
       </c>
@@ -43525,7 +43529,7 @@
       <c r="J21" s="7">
         <v>1</v>
       </c>
-      <c r="K21" s="123">
+      <c r="K21" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -43775,13 +43779,13 @@
       <c r="D22" s="61" t="s">
         <v>161</v>
       </c>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="119"/>
       <c r="G22" s="61"/>
       <c r="H22" s="61"/>
       <c r="I22" s="61"/>
       <c r="J22" s="61"/>
-      <c r="K22" s="123"/>
+      <c r="K22" s="96"/>
       <c r="L22" s="63" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -43948,8 +43952,8 @@
       <c r="D23" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E23" s="105"/>
-      <c r="F23" s="106"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
       <c r="G23" s="7">
         <v>1</v>
       </c>
@@ -43963,7 +43967,7 @@
       <c r="J23" s="7">
         <v>1</v>
       </c>
-      <c r="K23" s="123">
+      <c r="K23" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -44215,8 +44219,8 @@
       <c r="D24" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E24" s="105"/>
-      <c r="F24" s="106"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="119"/>
       <c r="G24" s="5">
         <v>1</v>
       </c>
@@ -44230,7 +44234,7 @@
       <c r="J24" s="5">
         <v>1</v>
       </c>
-      <c r="K24" s="123">
+      <c r="K24" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -44480,8 +44484,8 @@
       <c r="D25" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="E25" s="105"/>
-      <c r="F25" s="106"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="119"/>
       <c r="G25" s="7">
         <v>1</v>
       </c>
@@ -44495,7 +44499,7 @@
       <c r="J25" s="7">
         <v>1</v>
       </c>
-      <c r="K25" s="123">
+      <c r="K25" s="96">
         <f t="shared" si="15"/>
         <v>93</v>
       </c>
@@ -44747,8 +44751,8 @@
       <c r="D26" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="E26" s="107"/>
-      <c r="F26" s="108"/>
+      <c r="E26" s="120"/>
+      <c r="F26" s="121"/>
       <c r="G26" s="5">
         <v>1</v>
       </c>
@@ -44762,7 +44766,7 @@
       <c r="J26" s="5">
         <v>1</v>
       </c>
-      <c r="K26" s="123">
+      <c r="K26" s="96">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
@@ -45001,16 +45005,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E4:F26"/>
-    <mergeCell ref="P2:U2"/>
-    <mergeCell ref="V2:AA2"/>
-    <mergeCell ref="Q1:U1"/>
-    <mergeCell ref="V1:AA1"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AH1:AM1"/>
-    <mergeCell ref="AN1:AS1"/>
-    <mergeCell ref="AT1:AY1"/>
     <mergeCell ref="AZ1:BE1"/>
     <mergeCell ref="BF1:BK1"/>
     <mergeCell ref="AH2:AM2"/>
@@ -45018,6 +45012,16 @@
     <mergeCell ref="AT2:AY2"/>
     <mergeCell ref="AZ2:BE2"/>
     <mergeCell ref="BF2:BK2"/>
+    <mergeCell ref="AB1:AG1"/>
+    <mergeCell ref="AB2:AG2"/>
+    <mergeCell ref="AH1:AM1"/>
+    <mergeCell ref="AN1:AS1"/>
+    <mergeCell ref="AT1:AY1"/>
+    <mergeCell ref="E4:F26"/>
+    <mergeCell ref="P2:U2"/>
+    <mergeCell ref="V2:AA2"/>
+    <mergeCell ref="Q1:U1"/>
+    <mergeCell ref="V1:AA1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
@@ -47334,8 +47338,8 @@
       <c r="F3" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="G3" s="103"/>
-      <c r="H3" s="104"/>
+      <c r="G3" s="116"/>
+      <c r="H3" s="117"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -47401,8 +47405,8 @@
       <c r="F4" s="7" t="s">
         <v>586</v>
       </c>
-      <c r="G4" s="105"/>
-      <c r="H4" s="106"/>
+      <c r="G4" s="118"/>
+      <c r="H4" s="119"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
@@ -47468,8 +47472,8 @@
       <c r="F5" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="G5" s="105"/>
-      <c r="H5" s="106"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="119"/>
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -47535,8 +47539,8 @@
       <c r="F6" s="7" t="s">
         <v>578</v>
       </c>
-      <c r="G6" s="105"/>
-      <c r="H6" s="106"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="119"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
@@ -47600,8 +47604,8 @@
       <c r="F7" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="G7" s="105"/>
-      <c r="H7" s="106"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="119"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -47667,8 +47671,8 @@
       <c r="F8" s="7" t="s">
         <v>570</v>
       </c>
-      <c r="G8" s="105"/>
-      <c r="H8" s="106"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="119"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
@@ -47734,8 +47738,8 @@
       <c r="F9" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="119"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -47801,8 +47805,8 @@
       <c r="F10" s="7" t="s">
         <v>562</v>
       </c>
-      <c r="G10" s="105"/>
-      <c r="H10" s="106"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="119"/>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
@@ -47868,8 +47872,8 @@
       <c r="F11" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="G11" s="105"/>
-      <c r="H11" s="106"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="119"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -47935,8 +47939,8 @@
       <c r="F12" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="G12" s="105"/>
-      <c r="H12" s="106"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="119"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
@@ -48002,8 +48006,8 @@
       <c r="F13" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="G13" s="105"/>
-      <c r="H13" s="106"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="119"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -48067,8 +48071,8 @@
       <c r="F14" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="G14" s="105"/>
-      <c r="H14" s="106"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="119"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
@@ -48134,8 +48138,8 @@
       <c r="F15" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="G15" s="105"/>
-      <c r="H15" s="106"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="119"/>
       <c r="I15" s="5"/>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -48199,8 +48203,8 @@
       <c r="F16" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="G16" s="105"/>
-      <c r="H16" s="106"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="119"/>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
@@ -48266,8 +48270,8 @@
       <c r="F17" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="G17" s="105"/>
-      <c r="H17" s="106"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="119"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -48333,8 +48337,8 @@
       <c r="F18" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="G18" s="105"/>
-      <c r="H18" s="106"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="119"/>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
@@ -48400,8 +48404,8 @@
       <c r="F19" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="G19" s="105"/>
-      <c r="H19" s="106"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="119"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -48467,8 +48471,8 @@
       <c r="F20" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="106"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="119"/>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
       <c r="K20" s="7"/>
@@ -48534,8 +48538,8 @@
       <c r="F21" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="G21" s="105"/>
-      <c r="H21" s="106"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="119"/>
       <c r="I21" s="5"/>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -48599,8 +48603,8 @@
       <c r="F22" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="G22" s="105"/>
-      <c r="H22" s="106"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="119"/>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
@@ -48664,8 +48668,8 @@
       <c r="F23" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="G23" s="105"/>
-      <c r="H23" s="106"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="119"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -48731,8 +48735,8 @@
       <c r="F24" s="7" t="s">
         <v>506</v>
       </c>
-      <c r="G24" s="105"/>
-      <c r="H24" s="106"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="119"/>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
@@ -48798,8 +48802,8 @@
       <c r="F25" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="G25" s="105"/>
-      <c r="H25" s="106"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="119"/>
       <c r="I25" s="5"/>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -48865,8 +48869,8 @@
       <c r="F26" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="G26" s="105"/>
-      <c r="H26" s="106"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="119"/>
       <c r="I26" s="7"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
@@ -48930,8 +48934,8 @@
       <c r="F27" s="5" t="s">
         <v>494</v>
       </c>
-      <c r="G27" s="105"/>
-      <c r="H27" s="106"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="119"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -48997,8 +49001,8 @@
       <c r="F28" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="G28" s="105"/>
-      <c r="H28" s="106"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="119"/>
       <c r="I28" s="7"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
@@ -49064,8 +49068,8 @@
       <c r="F29" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="G29" s="105"/>
-      <c r="H29" s="106"/>
+      <c r="G29" s="118"/>
+      <c r="H29" s="119"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -49131,8 +49135,8 @@
       <c r="F30" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="G30" s="105"/>
-      <c r="H30" s="106"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="119"/>
       <c r="I30" s="7"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
@@ -49196,8 +49200,8 @@
       <c r="F31" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G31" s="105"/>
-      <c r="H31" s="106"/>
+      <c r="G31" s="118"/>
+      <c r="H31" s="119"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -49263,8 +49267,8 @@
       <c r="F32" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="G32" s="105"/>
-      <c r="H32" s="106"/>
+      <c r="G32" s="118"/>
+      <c r="H32" s="119"/>
       <c r="I32" s="7"/>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
@@ -49330,8 +49334,8 @@
       <c r="F33" s="5" t="s">
         <v>470</v>
       </c>
-      <c r="G33" s="105"/>
-      <c r="H33" s="106"/>
+      <c r="G33" s="118"/>
+      <c r="H33" s="119"/>
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -49397,8 +49401,8 @@
       <c r="F34" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="G34" s="105"/>
-      <c r="H34" s="106"/>
+      <c r="G34" s="118"/>
+      <c r="H34" s="119"/>
       <c r="I34" s="7"/>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -49464,8 +49468,8 @@
       <c r="F35" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="G35" s="105"/>
-      <c r="H35" s="106"/>
+      <c r="G35" s="118"/>
+      <c r="H35" s="119"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -49531,8 +49535,8 @@
       <c r="F36" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G36" s="105"/>
-      <c r="H36" s="106"/>
+      <c r="G36" s="118"/>
+      <c r="H36" s="119"/>
       <c r="I36" s="7"/>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
@@ -49598,8 +49602,8 @@
       <c r="F37" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="G37" s="105"/>
-      <c r="H37" s="106"/>
+      <c r="G37" s="118"/>
+      <c r="H37" s="119"/>
       <c r="I37" s="5"/>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -49665,8 +49669,8 @@
       <c r="F38" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="G38" s="105"/>
-      <c r="H38" s="106"/>
+      <c r="G38" s="118"/>
+      <c r="H38" s="119"/>
       <c r="I38" s="7"/>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
@@ -49732,8 +49736,8 @@
       <c r="F39" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="G39" s="105"/>
-      <c r="H39" s="106"/>
+      <c r="G39" s="118"/>
+      <c r="H39" s="119"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -49797,8 +49801,8 @@
       <c r="F40" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="G40" s="107"/>
-      <c r="H40" s="108"/>
+      <c r="G40" s="120"/>
+      <c r="H40" s="121"/>
       <c r="I40" s="7"/>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>

--- a/Asistencias/Calificaciones.xlsx
+++ b/Asistencias/Calificaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/carlosmartinez/Proyectos/Github/CalculoDiferencialTNM/Asistencias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A1C8266-F3F3-CF42-9A7C-6725C45B0624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7E55B2-C9C0-0244-80C3-AB488941826E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11920" yWindow="660" windowWidth="18240" windowHeight="17180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11920" yWindow="660" windowWidth="18240" windowHeight="17020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="5A_CD" sheetId="4" r:id="rId1"/>
